--- a/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_9.xlsx
+++ b/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_9.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\LApredict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227F1C6D-D435-4DDB-845E-7F44888B67DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14338F06-5597-4E18-AB99-2C6E6EB7C6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$P$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
-  <si>
-    <t>File</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Total Rows</t>
   </si>
@@ -78,336 +75,6 @@
   </si>
   <si>
     <t>Precision-Fault-prone</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_8_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_6_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_3_rep_5.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_9.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_1.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_0.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_3.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_2_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_1_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_4_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_2.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_0_rep_8.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_testset_rep_4.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_9_rep_7.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_7_rep_6.xlsx</t>
-  </si>
-  <si>
-    <t>U_predictions_ValidFold_5_rep_0.xlsx</t>
   </si>
   <si>
     <t>Recall</t>
@@ -790,9 +457,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q116"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -832,20 +499,17 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -859,6199 +523,5869 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>30</v>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1912</v>
       </c>
       <c r="B3">
-        <v>1912</v>
+        <v>1622</v>
       </c>
       <c r="C3">
-        <v>1622</v>
+        <v>1590</v>
       </c>
       <c r="D3">
-        <v>1590</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>681</v>
       </c>
       <c r="F3">
         <v>681</v>
       </c>
       <c r="G3">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>633</v>
       </c>
       <c r="I3">
         <v>633</v>
       </c>
       <c r="J3">
-        <v>633</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.92951541850220265</v>
       </c>
       <c r="L3">
         <v>0.92951541850220265</v>
       </c>
       <c r="M3">
-        <v>0.92951541850220265</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <f t="shared" ref="N3:N34" si="0">H3/B3</f>
+        <v>0.39025893958076446</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O34" si="0">I3/C3</f>
-        <v>0.39025893958076446</v>
+        <f t="shared" ref="O3:O34" si="1">I3/C3</f>
+        <v>0.39811320754716983</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P34" si="1">J3/D3</f>
-        <v>0.39811320754716983</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" ref="Q3:Q34" si="2">K3/E3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>61</v>
+        <f t="shared" ref="P3:P34" si="2">J3/D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1912</v>
       </c>
       <c r="B4">
-        <v>1912</v>
+        <v>1596</v>
       </c>
       <c r="C4">
-        <v>1596</v>
+        <v>1561</v>
       </c>
       <c r="D4">
-        <v>1561</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="F4">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G4">
-        <v>687</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>630</v>
       </c>
       <c r="I4">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J4">
-        <v>629</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0.91569767441860461</v>
       </c>
       <c r="L4">
-        <v>0.91569767441860461</v>
+        <v>0.9155749636098981</v>
       </c>
       <c r="M4">
-        <v>0.9155749636098981</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
         <f t="shared" si="0"/>
         <v>0.39473684210526316</v>
       </c>
-      <c r="P4">
+      <c r="O4">
         <f t="shared" si="1"/>
         <v>0.40294682895579759</v>
       </c>
-      <c r="Q4">
+      <c r="P4">
         <f t="shared" si="2"/>
         <v>2.8571428571428571E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>75</v>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1912</v>
       </c>
       <c r="B5">
-        <v>1912</v>
+        <v>1633</v>
       </c>
       <c r="C5">
-        <v>1633</v>
+        <v>1605</v>
       </c>
       <c r="D5">
-        <v>1605</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>728</v>
       </c>
       <c r="F5">
         <v>728</v>
       </c>
       <c r="G5">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="I5">
         <v>666</v>
       </c>
       <c r="J5">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.9148351648351648</v>
       </c>
       <c r="L5">
         <v>0.9148351648351648</v>
       </c>
       <c r="M5">
-        <v>0.9148351648351648</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
         <f t="shared" si="0"/>
         <v>0.40783833435394978</v>
       </c>
-      <c r="P5">
+      <c r="O5">
         <f t="shared" si="1"/>
         <v>0.41495327102803736</v>
       </c>
-      <c r="Q5">
+      <c r="P5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>81</v>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1912</v>
       </c>
       <c r="B6">
-        <v>1912</v>
+        <v>1630</v>
       </c>
       <c r="C6">
-        <v>1630</v>
+        <v>1592</v>
       </c>
       <c r="D6">
-        <v>1592</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>719</v>
       </c>
       <c r="F6">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G6">
-        <v>717</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>673</v>
       </c>
       <c r="I6">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J6">
-        <v>672</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0.93602225312934628</v>
       </c>
       <c r="L6">
-        <v>0.93602225312934628</v>
+        <v>0.93723849372384938</v>
       </c>
       <c r="M6">
-        <v>0.93723849372384938</v>
+        <v>0.5</v>
       </c>
       <c r="N6">
-        <v>0.5</v>
-      </c>
-      <c r="O6">
         <f t="shared" si="0"/>
         <v>0.41288343558282209</v>
       </c>
-      <c r="P6">
+      <c r="O6">
         <f t="shared" si="1"/>
         <v>0.42211055276381909</v>
       </c>
-      <c r="Q6">
+      <c r="P6">
         <f t="shared" si="2"/>
         <v>2.6315789473684209E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>84</v>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1912</v>
       </c>
       <c r="B7">
-        <v>1912</v>
+        <v>1612</v>
       </c>
       <c r="C7">
-        <v>1612</v>
+        <v>1577</v>
       </c>
       <c r="D7">
-        <v>1577</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>677</v>
       </c>
       <c r="F7">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G7">
-        <v>675</v>
+        <v>2</v>
       </c>
       <c r="H7">
+        <v>629</v>
+      </c>
+      <c r="I7">
+        <v>627</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>629</v>
-      </c>
-      <c r="J7">
-        <v>627</v>
-      </c>
       <c r="K7">
-        <v>2</v>
+        <v>0.92909896602658792</v>
       </c>
       <c r="L7">
-        <v>0.92909896602658792</v>
+        <v>0.92888888888888888</v>
       </c>
       <c r="M7">
-        <v>0.92888888888888888</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
         <f t="shared" si="0"/>
         <v>0.39019851116625309</v>
       </c>
-      <c r="P7">
+      <c r="O7">
         <f t="shared" si="1"/>
         <v>0.39759036144578314</v>
       </c>
-      <c r="Q7">
+      <c r="P7">
         <f t="shared" si="2"/>
         <v>5.7142857142857141E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>94</v>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1912</v>
       </c>
       <c r="B8">
-        <v>1912</v>
+        <v>1648</v>
       </c>
       <c r="C8">
-        <v>1648</v>
+        <v>1624</v>
       </c>
       <c r="D8">
-        <v>1624</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>651</v>
       </c>
       <c r="F8">
         <v>651</v>
       </c>
       <c r="G8">
-        <v>651</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="I8">
         <v>613</v>
       </c>
       <c r="J8">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.94162826420890933</v>
       </c>
       <c r="L8">
         <v>0.94162826420890933</v>
       </c>
       <c r="M8">
-        <v>0.94162826420890933</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
         <f t="shared" si="0"/>
         <v>0.3719660194174757</v>
       </c>
-      <c r="P8">
+      <c r="O8">
         <f t="shared" si="1"/>
         <v>0.37746305418719212</v>
       </c>
-      <c r="Q8">
+      <c r="P8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>108</v>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1912</v>
       </c>
       <c r="B9">
-        <v>1912</v>
+        <v>1625</v>
       </c>
       <c r="C9">
-        <v>1625</v>
+        <v>1603</v>
       </c>
       <c r="D9">
-        <v>1603</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>698</v>
       </c>
       <c r="F9">
         <v>698</v>
       </c>
       <c r="G9">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="I9">
         <v>640</v>
       </c>
       <c r="J9">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.91690544412607455</v>
       </c>
       <c r="L9">
         <v>0.91690544412607455</v>
       </c>
       <c r="M9">
-        <v>0.91690544412607455</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
         <f t="shared" si="0"/>
         <v>0.39384615384615385</v>
       </c>
-      <c r="P9">
+      <c r="O9">
         <f t="shared" si="1"/>
         <v>0.39925140361821587</v>
       </c>
-      <c r="Q9">
+      <c r="P9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>110</v>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1912</v>
       </c>
       <c r="B10">
-        <v>1912</v>
+        <v>1629</v>
       </c>
       <c r="C10">
-        <v>1629</v>
+        <v>1621</v>
       </c>
       <c r="D10">
-        <v>1621</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>727</v>
       </c>
       <c r="F10">
         <v>727</v>
       </c>
       <c r="G10">
-        <v>727</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="I10">
         <v>674</v>
       </c>
       <c r="J10">
-        <v>674</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.92709766162310869</v>
       </c>
       <c r="L10">
         <v>0.92709766162310869</v>
       </c>
       <c r="M10">
-        <v>0.92709766162310869</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
         <f t="shared" si="0"/>
         <v>0.41375076734192756</v>
       </c>
-      <c r="P10">
+      <c r="O10">
         <f t="shared" si="1"/>
         <v>0.41579272054287475</v>
       </c>
-      <c r="Q10">
+      <c r="P10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>111</v>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1912</v>
       </c>
       <c r="B11">
-        <v>1912</v>
+        <v>1633</v>
       </c>
       <c r="C11">
-        <v>1633</v>
+        <v>1603</v>
       </c>
       <c r="D11">
-        <v>1603</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>679</v>
       </c>
       <c r="F11">
         <v>679</v>
       </c>
       <c r="G11">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="I11">
         <v>637</v>
       </c>
       <c r="J11">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.93814432989690721</v>
       </c>
       <c r="L11">
         <v>0.93814432989690721</v>
       </c>
       <c r="M11">
-        <v>0.93814432989690721</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
         <f t="shared" si="0"/>
         <v>0.39007960808328229</v>
       </c>
-      <c r="P11">
+      <c r="O11">
         <f t="shared" si="1"/>
         <v>0.39737991266375544</v>
       </c>
-      <c r="Q11">
+      <c r="P11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>121</v>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1912</v>
       </c>
       <c r="B12">
-        <v>1912</v>
+        <v>1591</v>
       </c>
       <c r="C12">
-        <v>1591</v>
+        <v>1564</v>
       </c>
       <c r="D12">
-        <v>1564</v>
+        <v>27</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>724</v>
       </c>
       <c r="F12">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G12">
-        <v>723</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>657</v>
       </c>
       <c r="I12">
         <v>657</v>
       </c>
       <c r="J12">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>0.90745856353591159</v>
       </c>
       <c r="L12">
-        <v>0.90745856353591159</v>
+        <v>0.90871369294605808</v>
       </c>
       <c r="M12">
-        <v>0.90871369294605808</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
         <f t="shared" si="0"/>
         <v>0.41294783155248271</v>
       </c>
-      <c r="P12">
+      <c r="O12">
         <f t="shared" si="1"/>
         <v>0.42007672634271098</v>
       </c>
-      <c r="Q12">
+      <c r="P12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>15</v>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1913</v>
       </c>
       <c r="B13">
-        <v>1913</v>
+        <v>1635</v>
       </c>
       <c r="C13">
-        <v>1635</v>
+        <v>1608</v>
       </c>
       <c r="D13">
-        <v>1608</v>
+        <v>27</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>688</v>
       </c>
       <c r="F13">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G13">
-        <v>687</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>644</v>
       </c>
       <c r="I13">
         <v>644</v>
       </c>
       <c r="J13">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>0.93604651162790697</v>
       </c>
       <c r="L13">
-        <v>0.93604651162790697</v>
+        <v>0.93740902474526933</v>
       </c>
       <c r="M13">
-        <v>0.93740902474526933</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
         <f t="shared" si="0"/>
         <v>0.39388379204892965</v>
       </c>
-      <c r="P13">
+      <c r="O13">
         <f t="shared" si="1"/>
         <v>0.40049751243781095</v>
       </c>
-      <c r="Q13">
+      <c r="P13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>16</v>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1913</v>
       </c>
       <c r="B14">
-        <v>1913</v>
+        <v>1616</v>
       </c>
       <c r="C14">
-        <v>1616</v>
+        <v>1596</v>
       </c>
       <c r="D14">
-        <v>1596</v>
+        <v>20</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>717</v>
       </c>
       <c r="F14">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G14">
-        <v>716</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>665</v>
       </c>
       <c r="I14">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="J14">
-        <v>664</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0.92747559274755931</v>
       </c>
       <c r="L14">
-        <v>0.92747559274755931</v>
+        <v>0.92737430167597767</v>
       </c>
       <c r="M14">
-        <v>0.92737430167597767</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
         <f t="shared" si="0"/>
         <v>0.41150990099009899</v>
       </c>
-      <c r="P14">
+      <c r="O14">
         <f t="shared" si="1"/>
         <v>0.41604010025062654</v>
       </c>
-      <c r="Q14">
+      <c r="P14">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>17</v>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1913</v>
       </c>
       <c r="B15">
-        <v>1913</v>
+        <v>1607</v>
       </c>
       <c r="C15">
-        <v>1607</v>
+        <v>1589</v>
       </c>
       <c r="D15">
-        <v>1589</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>734</v>
       </c>
       <c r="F15">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="G15">
-        <v>732</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>676</v>
       </c>
       <c r="I15">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J15">
-        <v>675</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0.92098092643051777</v>
       </c>
       <c r="L15">
-        <v>0.92098092643051777</v>
+        <v>0.92213114754098358</v>
       </c>
       <c r="M15">
-        <v>0.92213114754098358</v>
+        <v>0.5</v>
       </c>
       <c r="N15">
-        <v>0.5</v>
-      </c>
-      <c r="O15">
         <f t="shared" si="0"/>
         <v>0.4206596141879278</v>
       </c>
-      <c r="P15">
+      <c r="O15">
         <f t="shared" si="1"/>
         <v>0.4247954688483323</v>
       </c>
-      <c r="Q15">
+      <c r="P15">
         <f t="shared" si="2"/>
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>18</v>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1913</v>
       </c>
       <c r="B16">
-        <v>1913</v>
+        <v>1589</v>
       </c>
       <c r="C16">
-        <v>1589</v>
+        <v>1563</v>
       </c>
       <c r="D16">
-        <v>1563</v>
+        <v>26</v>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>711</v>
       </c>
       <c r="F16">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G16">
-        <v>709</v>
+        <v>2</v>
       </c>
       <c r="H16">
+        <v>649</v>
+      </c>
+      <c r="I16">
+        <v>647</v>
+      </c>
+      <c r="J16">
         <v>2</v>
       </c>
-      <c r="I16">
-        <v>649</v>
-      </c>
-      <c r="J16">
-        <v>647</v>
-      </c>
       <c r="K16">
-        <v>2</v>
+        <v>0.91279887482419131</v>
       </c>
       <c r="L16">
-        <v>0.91279887482419131</v>
+        <v>0.91255289139633289</v>
       </c>
       <c r="M16">
-        <v>0.91255289139633289</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
         <f t="shared" si="0"/>
         <v>0.40843297671491502</v>
       </c>
-      <c r="P16">
+      <c r="O16">
         <f t="shared" si="1"/>
         <v>0.41394753678822777</v>
       </c>
-      <c r="Q16">
+      <c r="P16">
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>19</v>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1913</v>
       </c>
       <c r="B17">
-        <v>1913</v>
+        <v>1589</v>
       </c>
       <c r="C17">
-        <v>1589</v>
+        <v>1559</v>
       </c>
       <c r="D17">
-        <v>1559</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>684</v>
       </c>
       <c r="F17">
         <v>684</v>
       </c>
       <c r="G17">
-        <v>684</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="I17">
         <v>632</v>
       </c>
       <c r="J17">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>0.92397660818713445</v>
       </c>
       <c r="L17">
         <v>0.92397660818713445</v>
       </c>
       <c r="M17">
-        <v>0.92397660818713445</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
         <f t="shared" si="0"/>
         <v>0.39773442416614224</v>
       </c>
-      <c r="P17">
+      <c r="O17">
         <f t="shared" si="1"/>
         <v>0.4053880692751764</v>
       </c>
-      <c r="Q17">
+      <c r="P17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>20</v>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1913</v>
       </c>
       <c r="B18">
-        <v>1913</v>
+        <v>1577</v>
       </c>
       <c r="C18">
-        <v>1577</v>
+        <v>1543</v>
       </c>
       <c r="D18">
-        <v>1543</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>34</v>
+        <v>723</v>
       </c>
       <c r="F18">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="G18">
-        <v>718</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>666</v>
       </c>
       <c r="I18">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="J18">
-        <v>663</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>0.92116182572614103</v>
       </c>
       <c r="L18">
-        <v>0.92116182572614103</v>
+        <v>0.92339832869080785</v>
       </c>
       <c r="M18">
-        <v>0.92339832869080785</v>
+        <v>0.6</v>
       </c>
       <c r="N18">
-        <v>0.6</v>
-      </c>
-      <c r="O18">
         <f t="shared" si="0"/>
         <v>0.42232086239695626</v>
       </c>
-      <c r="P18">
+      <c r="O18">
         <f t="shared" si="1"/>
         <v>0.42968243681140633</v>
       </c>
-      <c r="Q18">
+      <c r="P18">
         <f t="shared" si="2"/>
         <v>8.8235294117647065E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>22</v>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1913</v>
       </c>
       <c r="B19">
-        <v>1913</v>
+        <v>1614</v>
       </c>
       <c r="C19">
-        <v>1614</v>
+        <v>1588</v>
       </c>
       <c r="D19">
-        <v>1588</v>
+        <v>26</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="F19">
         <v>665</v>
       </c>
       <c r="G19">
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="I19">
         <v>618</v>
       </c>
       <c r="J19">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>0.92932330827067666</v>
       </c>
       <c r="L19">
         <v>0.92932330827067666</v>
       </c>
       <c r="M19">
-        <v>0.92932330827067666</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
         <f t="shared" si="0"/>
         <v>0.38289962825278812</v>
       </c>
-      <c r="P19">
+      <c r="O19">
         <f t="shared" si="1"/>
         <v>0.38916876574307308</v>
       </c>
-      <c r="Q19">
+      <c r="P19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>23</v>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1913</v>
       </c>
       <c r="B20">
-        <v>1913</v>
+        <v>1642</v>
       </c>
       <c r="C20">
-        <v>1642</v>
+        <v>1629</v>
       </c>
       <c r="D20">
-        <v>1629</v>
+        <v>13</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>646</v>
       </c>
       <c r="F20">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G20">
-        <v>644</v>
+        <v>2</v>
       </c>
       <c r="H20">
+        <v>603</v>
+      </c>
+      <c r="I20">
+        <v>601</v>
+      </c>
+      <c r="J20">
         <v>2</v>
       </c>
-      <c r="I20">
-        <v>603</v>
-      </c>
-      <c r="J20">
-        <v>601</v>
-      </c>
       <c r="K20">
-        <v>2</v>
+        <v>0.93343653250773995</v>
       </c>
       <c r="L20">
-        <v>0.93343653250773995</v>
+        <v>0.93322981366459623</v>
       </c>
       <c r="M20">
-        <v>0.93322981366459623</v>
+        <v>1</v>
       </c>
       <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
         <f t="shared" si="0"/>
         <v>0.36723507917174175</v>
       </c>
-      <c r="P20">
+      <c r="O20">
         <f t="shared" si="1"/>
         <v>0.36893799877225292</v>
       </c>
-      <c r="Q20">
+      <c r="P20">
         <f t="shared" si="2"/>
         <v>0.15384615384615385</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>24</v>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1913</v>
       </c>
       <c r="B21">
-        <v>1913</v>
+        <v>1622</v>
       </c>
       <c r="C21">
-        <v>1622</v>
+        <v>1588</v>
       </c>
       <c r="D21">
-        <v>1588</v>
+        <v>34</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>679</v>
       </c>
       <c r="F21">
         <v>679</v>
       </c>
       <c r="G21">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="I21">
         <v>636</v>
       </c>
       <c r="J21">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>0.93667157584683358</v>
       </c>
       <c r="L21">
         <v>0.93667157584683358</v>
       </c>
       <c r="M21">
-        <v>0.93667157584683358</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
         <f t="shared" si="0"/>
         <v>0.39210850801479658</v>
       </c>
-      <c r="P21">
+      <c r="O21">
         <f t="shared" si="1"/>
         <v>0.40050377833753148</v>
       </c>
-      <c r="Q21">
+      <c r="P21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>25</v>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1913</v>
       </c>
       <c r="B22">
-        <v>1913</v>
+        <v>1609</v>
       </c>
       <c r="C22">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="D22">
-        <v>1594</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>714</v>
       </c>
       <c r="F22">
         <v>714</v>
       </c>
       <c r="G22">
-        <v>714</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="I22">
         <v>651</v>
       </c>
       <c r="J22">
-        <v>651</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>0.91176470588235292</v>
       </c>
       <c r="L22">
         <v>0.91176470588235292</v>
       </c>
       <c r="M22">
-        <v>0.91176470588235292</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
         <f t="shared" si="0"/>
         <v>0.40459912989434432</v>
       </c>
-      <c r="P22">
+      <c r="O22">
         <f t="shared" si="1"/>
         <v>0.4084065244667503</v>
       </c>
-      <c r="Q22">
+      <c r="P22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>26</v>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1913</v>
       </c>
       <c r="B23">
-        <v>1913</v>
+        <v>1602</v>
       </c>
       <c r="C23">
-        <v>1602</v>
+        <v>1571</v>
       </c>
       <c r="D23">
-        <v>1571</v>
+        <v>31</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>674</v>
       </c>
       <c r="F23">
         <v>674</v>
       </c>
       <c r="G23">
-        <v>674</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="I23">
         <v>631</v>
       </c>
       <c r="J23">
-        <v>631</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>0.93620178041543023</v>
       </c>
       <c r="L23">
         <v>0.93620178041543023</v>
       </c>
       <c r="M23">
-        <v>0.93620178041543023</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
         <f t="shared" si="0"/>
         <v>0.39388264669163547</v>
       </c>
-      <c r="P23">
+      <c r="O23">
         <f t="shared" si="1"/>
         <v>0.40165499681731381</v>
       </c>
-      <c r="Q23">
+      <c r="P23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>27</v>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1913</v>
       </c>
       <c r="B24">
-        <v>1913</v>
+        <v>1620</v>
       </c>
       <c r="C24">
-        <v>1620</v>
+        <v>1590</v>
       </c>
       <c r="D24">
-        <v>1590</v>
+        <v>30</v>
       </c>
       <c r="E24">
-        <v>30</v>
+        <v>660</v>
       </c>
       <c r="F24">
         <v>660</v>
       </c>
       <c r="G24">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="I24">
         <v>613</v>
       </c>
       <c r="J24">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>0.92878787878787883</v>
       </c>
       <c r="L24">
         <v>0.92878787878787883</v>
       </c>
       <c r="M24">
-        <v>0.92878787878787883</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
         <f t="shared" si="0"/>
         <v>0.37839506172839504</v>
       </c>
-      <c r="P24">
+      <c r="O24">
         <f t="shared" si="1"/>
         <v>0.38553459119496858</v>
       </c>
-      <c r="Q24">
+      <c r="P24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>28</v>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1913</v>
       </c>
       <c r="B25">
-        <v>1913</v>
+        <v>1631</v>
       </c>
       <c r="C25">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="D25">
-        <v>1622</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>653</v>
       </c>
       <c r="F25">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G25">
-        <v>651</v>
+        <v>2</v>
       </c>
       <c r="H25">
+        <v>613</v>
+      </c>
+      <c r="I25">
+        <v>611</v>
+      </c>
+      <c r="J25">
         <v>2</v>
       </c>
-      <c r="I25">
-        <v>613</v>
-      </c>
-      <c r="J25">
-        <v>611</v>
-      </c>
       <c r="K25">
-        <v>2</v>
+        <v>0.93874425727411948</v>
       </c>
       <c r="L25">
-        <v>0.93874425727411948</v>
+        <v>0.93855606758832566</v>
       </c>
       <c r="M25">
-        <v>0.93855606758832566</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
         <f t="shared" si="0"/>
         <v>0.37584304107909255</v>
       </c>
-      <c r="P25">
+      <c r="O25">
         <f t="shared" si="1"/>
         <v>0.37669543773119607</v>
       </c>
-      <c r="Q25">
+      <c r="P25">
         <f t="shared" si="2"/>
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>29</v>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1913</v>
       </c>
       <c r="B26">
-        <v>1913</v>
+        <v>1628</v>
       </c>
       <c r="C26">
-        <v>1628</v>
+        <v>1601</v>
       </c>
       <c r="D26">
-        <v>1601</v>
+        <v>27</v>
       </c>
       <c r="E26">
-        <v>27</v>
+        <v>742</v>
       </c>
       <c r="F26">
         <v>742</v>
       </c>
       <c r="G26">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="I26">
         <v>686</v>
       </c>
       <c r="J26">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>0.92452830188679247</v>
       </c>
       <c r="L26">
         <v>0.92452830188679247</v>
       </c>
       <c r="M26">
-        <v>0.92452830188679247</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
         <f t="shared" si="0"/>
         <v>0.42137592137592139</v>
       </c>
-      <c r="P26">
+      <c r="O26">
         <f t="shared" si="1"/>
         <v>0.42848219862585885</v>
       </c>
-      <c r="Q26">
+      <c r="P26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>31</v>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1913</v>
       </c>
       <c r="B27">
-        <v>1913</v>
+        <v>1603</v>
       </c>
       <c r="C27">
-        <v>1603</v>
+        <v>1579</v>
       </c>
       <c r="D27">
-        <v>1579</v>
+        <v>24</v>
       </c>
       <c r="E27">
-        <v>24</v>
+        <v>694</v>
       </c>
       <c r="F27">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G27">
-        <v>692</v>
+        <v>2</v>
       </c>
       <c r="H27">
+        <v>642</v>
+      </c>
+      <c r="I27">
+        <v>640</v>
+      </c>
+      <c r="J27">
         <v>2</v>
       </c>
-      <c r="I27">
-        <v>642</v>
-      </c>
-      <c r="J27">
-        <v>640</v>
-      </c>
       <c r="K27">
-        <v>2</v>
+        <v>0.9250720461095101</v>
       </c>
       <c r="L27">
-        <v>0.9250720461095101</v>
+        <v>0.92485549132947975</v>
       </c>
       <c r="M27">
-        <v>0.92485549132947975</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
         <f t="shared" si="0"/>
         <v>0.40049906425452275</v>
       </c>
-      <c r="P27">
+      <c r="O27">
         <f t="shared" si="1"/>
         <v>0.4053198226725776</v>
       </c>
-      <c r="Q27">
+      <c r="P27">
         <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>32</v>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>1913</v>
       </c>
       <c r="B28">
-        <v>1913</v>
+        <v>1617</v>
       </c>
       <c r="C28">
-        <v>1617</v>
+        <v>1590</v>
       </c>
       <c r="D28">
-        <v>1590</v>
+        <v>27</v>
       </c>
       <c r="E28">
-        <v>27</v>
+        <v>692</v>
       </c>
       <c r="F28">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G28">
-        <v>690</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>646</v>
       </c>
       <c r="I28">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J28">
-        <v>645</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>0.93352601156069359</v>
       </c>
       <c r="L28">
-        <v>0.93352601156069359</v>
+        <v>0.93478260869565222</v>
       </c>
       <c r="M28">
-        <v>0.93478260869565222</v>
+        <v>0.5</v>
       </c>
       <c r="N28">
-        <v>0.5</v>
-      </c>
-      <c r="O28">
         <f t="shared" si="0"/>
         <v>0.39950525664811382</v>
       </c>
-      <c r="P28">
+      <c r="O28">
         <f t="shared" si="1"/>
         <v>0.40566037735849059</v>
       </c>
-      <c r="Q28">
+      <c r="P28">
         <f t="shared" si="2"/>
         <v>3.7037037037037035E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>33</v>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1913</v>
       </c>
       <c r="B29">
-        <v>1913</v>
+        <v>1586</v>
       </c>
       <c r="C29">
-        <v>1586</v>
+        <v>1552</v>
       </c>
       <c r="D29">
-        <v>1552</v>
+        <v>34</v>
       </c>
       <c r="E29">
-        <v>34</v>
+        <v>697</v>
       </c>
       <c r="F29">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G29">
-        <v>696</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>639</v>
       </c>
       <c r="I29">
         <v>639</v>
       </c>
       <c r="J29">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>0.91678622668579624</v>
       </c>
       <c r="L29">
-        <v>0.91678622668579624</v>
+        <v>0.9181034482758621</v>
       </c>
       <c r="M29">
-        <v>0.9181034482758621</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
         <f t="shared" si="0"/>
         <v>0.40290037831021436</v>
       </c>
-      <c r="P29">
+      <c r="O29">
         <f t="shared" si="1"/>
         <v>0.41172680412371132</v>
       </c>
-      <c r="Q29">
+      <c r="P29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1913</v>
+      </c>
+      <c r="B30">
+        <v>1616</v>
+      </c>
+      <c r="C30">
+        <v>1582</v>
+      </c>
+      <c r="D30">
         <v>34</v>
       </c>
-      <c r="B30">
-        <v>1913</v>
-      </c>
-      <c r="C30">
-        <v>1616</v>
-      </c>
-      <c r="D30">
-        <v>1582</v>
-      </c>
       <c r="E30">
-        <v>34</v>
+        <v>660</v>
       </c>
       <c r="F30">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G30">
-        <v>657</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>612</v>
       </c>
       <c r="I30">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J30">
-        <v>611</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>0.92727272727272725</v>
       </c>
       <c r="L30">
-        <v>0.92727272727272725</v>
+        <v>0.9299847792998478</v>
       </c>
       <c r="M30">
-        <v>0.9299847792998478</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N30">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="O30">
         <f t="shared" si="0"/>
         <v>0.37871287128712872</v>
       </c>
-      <c r="P30">
+      <c r="O30">
         <f t="shared" si="1"/>
         <v>0.38621997471554992</v>
       </c>
-      <c r="Q30">
+      <c r="P30">
         <f t="shared" si="2"/>
         <v>2.9411764705882353E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>35</v>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1913</v>
       </c>
       <c r="B31">
-        <v>1913</v>
+        <v>1614</v>
       </c>
       <c r="C31">
-        <v>1614</v>
+        <v>1589</v>
       </c>
       <c r="D31">
-        <v>1589</v>
+        <v>25</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>669</v>
       </c>
       <c r="F31">
         <v>669</v>
       </c>
       <c r="G31">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="I31">
         <v>626</v>
       </c>
       <c r="J31">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>0.93572496263079219</v>
       </c>
       <c r="L31">
         <v>0.93572496263079219</v>
       </c>
       <c r="M31">
-        <v>0.93572496263079219</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
         <f t="shared" si="0"/>
         <v>0.38785625774473359</v>
       </c>
-      <c r="P31">
+      <c r="O31">
         <f t="shared" si="1"/>
         <v>0.39395846444304594</v>
       </c>
-      <c r="Q31">
+      <c r="P31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>36</v>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>1913</v>
       </c>
       <c r="B32">
-        <v>1913</v>
+        <v>1620</v>
       </c>
       <c r="C32">
-        <v>1620</v>
+        <v>1592</v>
       </c>
       <c r="D32">
-        <v>1592</v>
+        <v>28</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>670</v>
       </c>
       <c r="F32">
         <v>670</v>
       </c>
       <c r="G32">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="I32">
         <v>621</v>
       </c>
       <c r="J32">
-        <v>621</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>0.92686567164179101</v>
       </c>
       <c r="L32">
         <v>0.92686567164179101</v>
       </c>
       <c r="M32">
-        <v>0.92686567164179101</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
         <f t="shared" si="0"/>
         <v>0.38333333333333336</v>
       </c>
-      <c r="P32">
+      <c r="O32">
         <f t="shared" si="1"/>
         <v>0.39007537688442212</v>
       </c>
-      <c r="Q32">
+      <c r="P32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>37</v>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>1913</v>
       </c>
       <c r="B33">
-        <v>1913</v>
+        <v>1601</v>
       </c>
       <c r="C33">
-        <v>1601</v>
+        <v>1571</v>
       </c>
       <c r="D33">
-        <v>1571</v>
+        <v>30</v>
       </c>
       <c r="E33">
-        <v>30</v>
+        <v>775</v>
       </c>
       <c r="F33">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G33">
-        <v>774</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>699</v>
       </c>
       <c r="I33">
         <v>699</v>
       </c>
       <c r="J33">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>0.90193548387096778</v>
       </c>
       <c r="L33">
-        <v>0.90193548387096778</v>
+        <v>0.9031007751937985</v>
       </c>
       <c r="M33">
-        <v>0.9031007751937985</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
         <f t="shared" si="0"/>
         <v>0.43660212367270457</v>
       </c>
-      <c r="P33">
+      <c r="O33">
         <f t="shared" si="1"/>
         <v>0.44493952896244432</v>
       </c>
-      <c r="Q33">
+      <c r="P33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>38</v>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>1913</v>
       </c>
       <c r="B34">
-        <v>1913</v>
+        <v>1623</v>
       </c>
       <c r="C34">
-        <v>1623</v>
+        <v>1587</v>
       </c>
       <c r="D34">
-        <v>1587</v>
+        <v>36</v>
       </c>
       <c r="E34">
-        <v>36</v>
+        <v>703</v>
       </c>
       <c r="F34">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G34">
-        <v>701</v>
+        <v>2</v>
       </c>
       <c r="H34">
+        <v>653</v>
+      </c>
+      <c r="I34">
+        <v>651</v>
+      </c>
+      <c r="J34">
         <v>2</v>
       </c>
-      <c r="I34">
-        <v>653</v>
-      </c>
-      <c r="J34">
-        <v>651</v>
-      </c>
       <c r="K34">
-        <v>2</v>
+        <v>0.92887624466571839</v>
       </c>
       <c r="L34">
-        <v>0.92887624466571839</v>
+        <v>0.92867332382310985</v>
       </c>
       <c r="M34">
-        <v>0.92867332382310985</v>
+        <v>1</v>
       </c>
       <c r="N34">
-        <v>1</v>
-      </c>
-      <c r="O34">
         <f t="shared" si="0"/>
         <v>0.40234134319162046</v>
       </c>
-      <c r="P34">
+      <c r="O34">
         <f t="shared" si="1"/>
         <v>0.41020793950850659</v>
       </c>
-      <c r="Q34">
+      <c r="P34">
         <f t="shared" si="2"/>
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>39</v>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>1913</v>
       </c>
       <c r="B35">
-        <v>1913</v>
+        <v>1609</v>
       </c>
       <c r="C35">
-        <v>1609</v>
+        <v>1577</v>
       </c>
       <c r="D35">
-        <v>1577</v>
+        <v>32</v>
       </c>
       <c r="E35">
-        <v>32</v>
+        <v>692</v>
       </c>
       <c r="F35">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G35">
-        <v>691</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>643</v>
       </c>
       <c r="I35">
         <v>643</v>
       </c>
       <c r="J35">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>0.92919075144508667</v>
       </c>
       <c r="L35">
-        <v>0.92919075144508667</v>
+        <v>0.93053545586107089</v>
       </c>
       <c r="M35">
-        <v>0.93053545586107089</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <f t="shared" ref="N35:N66" si="3">H35/B35</f>
+        <v>0.39962709757613424</v>
       </c>
       <c r="O35">
-        <f t="shared" ref="O35:O66" si="3">I35/C35</f>
-        <v>0.39962709757613424</v>
+        <f t="shared" ref="O35:O66" si="4">I35/C35</f>
+        <v>0.40773620798985416</v>
       </c>
       <c r="P35">
-        <f t="shared" ref="P35:P66" si="4">J35/D35</f>
-        <v>0.40773620798985416</v>
-      </c>
-      <c r="Q35">
-        <f t="shared" ref="Q35:Q66" si="5">K35/E35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>40</v>
+        <f t="shared" ref="P35:P66" si="5">J35/D35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1913</v>
       </c>
       <c r="B36">
-        <v>1913</v>
+        <v>1617</v>
       </c>
       <c r="C36">
-        <v>1617</v>
+        <v>1593</v>
       </c>
       <c r="D36">
-        <v>1593</v>
+        <v>24</v>
       </c>
       <c r="E36">
-        <v>24</v>
+        <v>690</v>
       </c>
       <c r="F36">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G36">
-        <v>689</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>634</v>
       </c>
       <c r="I36">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J36">
-        <v>633</v>
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>0.91884057971014488</v>
       </c>
       <c r="L36">
-        <v>0.91884057971014488</v>
+        <v>0.91872278664731499</v>
       </c>
       <c r="M36">
-        <v>0.91872278664731499</v>
+        <v>1</v>
       </c>
       <c r="N36">
-        <v>1</v>
-      </c>
-      <c r="O36">
         <f t="shared" si="3"/>
         <v>0.39208410636982066</v>
       </c>
-      <c r="P36">
+      <c r="O36">
         <f t="shared" si="4"/>
         <v>0.39736346516007531</v>
       </c>
-      <c r="Q36">
+      <c r="P36">
         <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>41</v>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>1913</v>
       </c>
       <c r="B37">
-        <v>1913</v>
+        <v>1642</v>
       </c>
       <c r="C37">
-        <v>1642</v>
+        <v>1614</v>
       </c>
       <c r="D37">
-        <v>1614</v>
+        <v>28</v>
       </c>
       <c r="E37">
-        <v>28</v>
+        <v>619</v>
       </c>
       <c r="F37">
         <v>619</v>
       </c>
       <c r="G37">
-        <v>619</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="I37">
         <v>579</v>
       </c>
       <c r="J37">
-        <v>579</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>0.93537964458804523</v>
       </c>
       <c r="L37">
         <v>0.93537964458804523</v>
       </c>
       <c r="M37">
-        <v>0.93537964458804523</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
         <f t="shared" si="3"/>
         <v>0.35261875761266748</v>
       </c>
-      <c r="P37">
+      <c r="O37">
         <f t="shared" si="4"/>
         <v>0.35873605947955389</v>
       </c>
-      <c r="Q37">
+      <c r="P37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>43</v>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>1913</v>
       </c>
       <c r="B38">
-        <v>1913</v>
+        <v>1597</v>
       </c>
       <c r="C38">
-        <v>1597</v>
+        <v>1566</v>
       </c>
       <c r="D38">
-        <v>1566</v>
+        <v>31</v>
       </c>
       <c r="E38">
-        <v>31</v>
+        <v>745</v>
       </c>
       <c r="F38">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G38">
-        <v>744</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>681</v>
       </c>
       <c r="I38">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J38">
-        <v>680</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>0.91409395973154361</v>
       </c>
       <c r="L38">
-        <v>0.91409395973154361</v>
+        <v>0.91397849462365588</v>
       </c>
       <c r="M38">
-        <v>0.91397849462365588</v>
+        <v>1</v>
       </c>
       <c r="N38">
-        <v>1</v>
-      </c>
-      <c r="O38">
         <f t="shared" si="3"/>
         <v>0.42642454602379459</v>
       </c>
-      <c r="P38">
+      <c r="O38">
         <f t="shared" si="4"/>
         <v>0.4342273307790549</v>
       </c>
-      <c r="Q38">
+      <c r="P38">
         <f t="shared" si="5"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>44</v>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>1913</v>
       </c>
       <c r="B39">
-        <v>1913</v>
+        <v>1616</v>
       </c>
       <c r="C39">
-        <v>1616</v>
+        <v>1610</v>
       </c>
       <c r="D39">
-        <v>1610</v>
+        <v>6</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>713</v>
       </c>
       <c r="F39">
         <v>713</v>
       </c>
       <c r="G39">
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>662</v>
       </c>
       <c r="I39">
         <v>662</v>
       </c>
       <c r="J39">
-        <v>662</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>0.92847124824684435</v>
       </c>
       <c r="L39">
         <v>0.92847124824684435</v>
       </c>
       <c r="M39">
-        <v>0.92847124824684435</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
         <f t="shared" si="3"/>
         <v>0.40965346534653463</v>
       </c>
-      <c r="P39">
+      <c r="O39">
         <f t="shared" si="4"/>
         <v>0.41118012422360251</v>
       </c>
-      <c r="Q39">
+      <c r="P39">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>45</v>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1913</v>
       </c>
       <c r="B40">
-        <v>1913</v>
+        <v>1626</v>
       </c>
       <c r="C40">
-        <v>1626</v>
+        <v>1594</v>
       </c>
       <c r="D40">
-        <v>1594</v>
+        <v>32</v>
       </c>
       <c r="E40">
-        <v>32</v>
+        <v>716</v>
       </c>
       <c r="F40">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G40">
-        <v>715</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>670</v>
       </c>
       <c r="I40">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J40">
-        <v>669</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>0.93575418994413406</v>
       </c>
       <c r="L40">
-        <v>0.93575418994413406</v>
+        <v>0.93566433566433571</v>
       </c>
       <c r="M40">
-        <v>0.93566433566433571</v>
+        <v>1</v>
       </c>
       <c r="N40">
-        <v>1</v>
-      </c>
-      <c r="O40">
         <f t="shared" si="3"/>
         <v>0.41205412054120544</v>
       </c>
-      <c r="P40">
+      <c r="O40">
         <f t="shared" si="4"/>
         <v>0.41969887076537016</v>
       </c>
-      <c r="Q40">
+      <c r="P40">
         <f t="shared" si="5"/>
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>46</v>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>1913</v>
       </c>
       <c r="B41">
-        <v>1913</v>
+        <v>1635</v>
       </c>
       <c r="C41">
-        <v>1635</v>
+        <v>1602</v>
       </c>
       <c r="D41">
-        <v>1602</v>
+        <v>33</v>
       </c>
       <c r="E41">
-        <v>33</v>
+        <v>690</v>
       </c>
       <c r="F41">
         <v>690</v>
       </c>
       <c r="G41">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="I41">
         <v>643</v>
       </c>
       <c r="J41">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>0.93188405797101448</v>
       </c>
       <c r="L41">
         <v>0.93188405797101448</v>
       </c>
       <c r="M41">
-        <v>0.93188405797101448</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
         <f t="shared" si="3"/>
         <v>0.39327217125382263</v>
       </c>
-      <c r="P41">
+      <c r="O41">
         <f t="shared" si="4"/>
         <v>0.40137328339575529</v>
       </c>
-      <c r="Q41">
+      <c r="P41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>47</v>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1913</v>
       </c>
       <c r="B42">
-        <v>1913</v>
+        <v>1619</v>
       </c>
       <c r="C42">
-        <v>1619</v>
+        <v>1586</v>
       </c>
       <c r="D42">
-        <v>1586</v>
+        <v>33</v>
       </c>
       <c r="E42">
-        <v>33</v>
+        <v>664</v>
       </c>
       <c r="F42">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G42">
-        <v>662</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>620</v>
       </c>
       <c r="I42">
         <v>620</v>
       </c>
       <c r="J42">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>0.9337349397590361</v>
       </c>
       <c r="L42">
-        <v>0.9337349397590361</v>
+        <v>0.93655589123867067</v>
       </c>
       <c r="M42">
-        <v>0.93655589123867067</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
         <f t="shared" si="3"/>
         <v>0.38295243977764054</v>
       </c>
-      <c r="P42">
+      <c r="O42">
         <f t="shared" si="4"/>
         <v>0.39092055485498106</v>
       </c>
-      <c r="Q42">
+      <c r="P42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>48</v>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>1913</v>
       </c>
       <c r="B43">
-        <v>1913</v>
+        <v>1619</v>
       </c>
       <c r="C43">
-        <v>1619</v>
+        <v>1589</v>
       </c>
       <c r="D43">
-        <v>1589</v>
+        <v>30</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>734</v>
       </c>
       <c r="F43">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G43">
-        <v>733</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>690</v>
       </c>
       <c r="I43">
         <v>690</v>
       </c>
       <c r="J43">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>0.94005449591280654</v>
       </c>
       <c r="L43">
-        <v>0.94005449591280654</v>
+        <v>0.94133697135061389</v>
       </c>
       <c r="M43">
-        <v>0.94133697135061389</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
         <f t="shared" si="3"/>
         <v>0.42618900555898703</v>
       </c>
-      <c r="P43">
+      <c r="O43">
         <f t="shared" si="4"/>
         <v>0.434235368156073</v>
       </c>
-      <c r="Q43">
+      <c r="P43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>50</v>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1913</v>
       </c>
       <c r="B44">
-        <v>1913</v>
+        <v>1625</v>
       </c>
       <c r="C44">
-        <v>1625</v>
+        <v>1601</v>
       </c>
       <c r="D44">
-        <v>1601</v>
+        <v>24</v>
       </c>
       <c r="E44">
-        <v>24</v>
+        <v>710</v>
       </c>
       <c r="F44">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G44">
-        <v>708</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>657</v>
       </c>
       <c r="I44">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J44">
-        <v>656</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>1</v>
+        <v>0.92535211267605633</v>
       </c>
       <c r="L44">
-        <v>0.92535211267605633</v>
+        <v>0.92655367231638419</v>
       </c>
       <c r="M44">
-        <v>0.92655367231638419</v>
+        <v>0.5</v>
       </c>
       <c r="N44">
-        <v>0.5</v>
-      </c>
-      <c r="O44">
         <f t="shared" si="3"/>
         <v>0.40430769230769231</v>
       </c>
-      <c r="P44">
+      <c r="O44">
         <f t="shared" si="4"/>
         <v>0.40974391005621486</v>
       </c>
-      <c r="Q44">
+      <c r="P44">
         <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>51</v>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>1913</v>
       </c>
       <c r="B45">
-        <v>1913</v>
+        <v>1610</v>
       </c>
       <c r="C45">
-        <v>1610</v>
+        <v>1587</v>
       </c>
       <c r="D45">
-        <v>1587</v>
+        <v>23</v>
       </c>
       <c r="E45">
-        <v>23</v>
+        <v>688</v>
       </c>
       <c r="F45">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G45">
-        <v>686</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>629</v>
       </c>
       <c r="I45">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J45">
-        <v>628</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0.91424418604651159</v>
       </c>
       <c r="L45">
-        <v>0.91424418604651159</v>
+        <v>0.91545189504373181</v>
       </c>
       <c r="M45">
-        <v>0.91545189504373181</v>
+        <v>0.5</v>
       </c>
       <c r="N45">
-        <v>0.5</v>
-      </c>
-      <c r="O45">
         <f t="shared" si="3"/>
         <v>0.3906832298136646</v>
       </c>
-      <c r="P45">
+      <c r="O45">
         <f t="shared" si="4"/>
         <v>0.39571518588531823</v>
       </c>
-      <c r="Q45">
+      <c r="P45">
         <f t="shared" si="5"/>
         <v>4.3478260869565216E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>52</v>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1913</v>
       </c>
       <c r="B46">
-        <v>1913</v>
+        <v>1592</v>
       </c>
       <c r="C46">
-        <v>1592</v>
+        <v>1570</v>
       </c>
       <c r="D46">
-        <v>1570</v>
+        <v>22</v>
       </c>
       <c r="E46">
-        <v>22</v>
+        <v>668</v>
       </c>
       <c r="F46">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G46">
-        <v>667</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>618</v>
       </c>
       <c r="I46">
         <v>618</v>
       </c>
       <c r="J46">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>0.92514970059880242</v>
       </c>
       <c r="L46">
-        <v>0.92514970059880242</v>
+        <v>0.92653673163418293</v>
       </c>
       <c r="M46">
-        <v>0.92653673163418293</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
         <f t="shared" si="3"/>
         <v>0.38819095477386933</v>
       </c>
-      <c r="P46">
+      <c r="O46">
         <f t="shared" si="4"/>
         <v>0.39363057324840767</v>
       </c>
-      <c r="Q46">
+      <c r="P46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>54</v>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>1913</v>
       </c>
       <c r="B47">
-        <v>1913</v>
+        <v>1637</v>
       </c>
       <c r="C47">
-        <v>1637</v>
+        <v>1606</v>
       </c>
       <c r="D47">
-        <v>1606</v>
+        <v>31</v>
       </c>
       <c r="E47">
-        <v>31</v>
+        <v>651</v>
       </c>
       <c r="F47">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G47">
-        <v>649</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>608</v>
       </c>
       <c r="I47">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J47">
-        <v>607</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>0.9339477726574501</v>
       </c>
       <c r="L47">
-        <v>0.9339477726574501</v>
+        <v>0.93528505392912176</v>
       </c>
       <c r="M47">
-        <v>0.93528505392912176</v>
+        <v>0.5</v>
       </c>
       <c r="N47">
-        <v>0.5</v>
-      </c>
-      <c r="O47">
         <f t="shared" si="3"/>
         <v>0.37141111789859499</v>
       </c>
-      <c r="P47">
+      <c r="O47">
         <f t="shared" si="4"/>
         <v>0.3779576587795766</v>
       </c>
-      <c r="Q47">
+      <c r="P47">
         <f t="shared" si="5"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>56</v>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1913</v>
       </c>
       <c r="B48">
-        <v>1913</v>
+        <v>1621</v>
       </c>
       <c r="C48">
-        <v>1621</v>
+        <v>1599</v>
       </c>
       <c r="D48">
-        <v>1599</v>
+        <v>22</v>
       </c>
       <c r="E48">
-        <v>22</v>
+        <v>689</v>
       </c>
       <c r="F48">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G48">
-        <v>688</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>641</v>
       </c>
       <c r="I48">
         <v>641</v>
       </c>
       <c r="J48">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>0.93033381712626995</v>
       </c>
       <c r="L48">
-        <v>0.93033381712626995</v>
+        <v>0.9316860465116279</v>
       </c>
       <c r="M48">
-        <v>0.9316860465116279</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
         <f t="shared" si="3"/>
         <v>0.39543491671807524</v>
       </c>
-      <c r="P48">
+      <c r="O48">
         <f t="shared" si="4"/>
         <v>0.40087554721701063</v>
       </c>
-      <c r="Q48">
+      <c r="P48">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>57</v>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>1913</v>
       </c>
       <c r="B49">
-        <v>1913</v>
+        <v>1622</v>
       </c>
       <c r="C49">
-        <v>1622</v>
+        <v>1592</v>
       </c>
       <c r="D49">
-        <v>1592</v>
+        <v>30</v>
       </c>
       <c r="E49">
-        <v>30</v>
+        <v>728</v>
       </c>
       <c r="F49">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G49">
-        <v>727</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>676</v>
       </c>
       <c r="I49">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J49">
-        <v>675</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="L49">
-        <v>0.9285714285714286</v>
+        <v>0.92847317744154056</v>
       </c>
       <c r="M49">
-        <v>0.92847317744154056</v>
+        <v>1</v>
       </c>
       <c r="N49">
-        <v>1</v>
-      </c>
-      <c r="O49">
         <f t="shared" si="3"/>
         <v>0.41676942046855736</v>
       </c>
-      <c r="P49">
+      <c r="O49">
         <f t="shared" si="4"/>
         <v>0.42399497487437188</v>
       </c>
-      <c r="Q49">
+      <c r="P49">
         <f t="shared" si="5"/>
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>58</v>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>1913</v>
       </c>
       <c r="B50">
-        <v>1913</v>
+        <v>1614</v>
       </c>
       <c r="C50">
-        <v>1614</v>
+        <v>1584</v>
       </c>
       <c r="D50">
-        <v>1584</v>
+        <v>30</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>640</v>
       </c>
       <c r="F50">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G50">
-        <v>638</v>
+        <v>2</v>
       </c>
       <c r="H50">
+        <v>594</v>
+      </c>
+      <c r="I50">
+        <v>592</v>
+      </c>
+      <c r="J50">
         <v>2</v>
       </c>
-      <c r="I50">
-        <v>594</v>
-      </c>
-      <c r="J50">
-        <v>592</v>
-      </c>
       <c r="K50">
-        <v>2</v>
+        <v>0.92812499999999998</v>
       </c>
       <c r="L50">
-        <v>0.92812499999999998</v>
+        <v>0.92789968652037613</v>
       </c>
       <c r="M50">
-        <v>0.92789968652037613</v>
+        <v>1</v>
       </c>
       <c r="N50">
-        <v>1</v>
-      </c>
-      <c r="O50">
         <f t="shared" si="3"/>
         <v>0.36802973977695169</v>
       </c>
-      <c r="P50">
+      <c r="O50">
         <f t="shared" si="4"/>
         <v>0.37373737373737376</v>
       </c>
-      <c r="Q50">
+      <c r="P50">
         <f t="shared" si="5"/>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>59</v>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1913</v>
       </c>
       <c r="B51">
-        <v>1913</v>
+        <v>1611</v>
       </c>
       <c r="C51">
-        <v>1611</v>
+        <v>1583</v>
       </c>
       <c r="D51">
-        <v>1583</v>
+        <v>28</v>
       </c>
       <c r="E51">
-        <v>28</v>
+        <v>727</v>
       </c>
       <c r="F51">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G51">
-        <v>726</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>667</v>
       </c>
       <c r="I51">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J51">
-        <v>666</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>0.91746905089408526</v>
       </c>
       <c r="L51">
-        <v>0.91746905089408526</v>
+        <v>0.9173553719008265</v>
       </c>
       <c r="M51">
-        <v>0.9173553719008265</v>
+        <v>1</v>
       </c>
       <c r="N51">
-        <v>1</v>
-      </c>
-      <c r="O51">
         <f t="shared" si="3"/>
         <v>0.41402855369335817</v>
       </c>
-      <c r="P51">
+      <c r="O51">
         <f t="shared" si="4"/>
         <v>0.42072015161086546</v>
       </c>
-      <c r="Q51">
+      <c r="P51">
         <f t="shared" si="5"/>
         <v>3.5714285714285712E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>60</v>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>1913</v>
       </c>
       <c r="B52">
-        <v>1913</v>
+        <v>1628</v>
       </c>
       <c r="C52">
-        <v>1628</v>
+        <v>1596</v>
       </c>
       <c r="D52">
-        <v>1596</v>
+        <v>32</v>
       </c>
       <c r="E52">
-        <v>32</v>
+        <v>657</v>
       </c>
       <c r="F52">
         <v>657</v>
       </c>
       <c r="G52">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="I52">
         <v>613</v>
       </c>
       <c r="J52">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>0.9330289193302892</v>
       </c>
       <c r="L52">
         <v>0.9330289193302892</v>
       </c>
       <c r="M52">
-        <v>0.9330289193302892</v>
+        <v>0</v>
       </c>
       <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
         <f t="shared" si="3"/>
         <v>0.37653562653562656</v>
       </c>
-      <c r="P52">
+      <c r="O52">
         <f t="shared" si="4"/>
         <v>0.38408521303258147</v>
       </c>
-      <c r="Q52">
+      <c r="P52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>62</v>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>1913</v>
       </c>
       <c r="B53">
-        <v>1913</v>
+        <v>1620</v>
       </c>
       <c r="C53">
-        <v>1620</v>
+        <v>1586</v>
       </c>
       <c r="D53">
-        <v>1586</v>
+        <v>34</v>
       </c>
       <c r="E53">
-        <v>34</v>
+        <v>691</v>
       </c>
       <c r="F53">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G53">
-        <v>688</v>
+        <v>3</v>
       </c>
       <c r="H53">
+        <v>641</v>
+      </c>
+      <c r="I53">
+        <v>638</v>
+      </c>
+      <c r="J53">
         <v>3</v>
       </c>
-      <c r="I53">
-        <v>641</v>
-      </c>
-      <c r="J53">
-        <v>638</v>
-      </c>
       <c r="K53">
-        <v>3</v>
+        <v>0.9276410998552822</v>
       </c>
       <c r="L53">
-        <v>0.9276410998552822</v>
+        <v>0.92732558139534882</v>
       </c>
       <c r="M53">
-        <v>0.92732558139534882</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>1</v>
-      </c>
-      <c r="O53">
         <f t="shared" si="3"/>
         <v>0.39567901234567904</v>
       </c>
-      <c r="P53">
+      <c r="O53">
         <f t="shared" si="4"/>
         <v>0.40226986128625475</v>
       </c>
-      <c r="Q53">
+      <c r="P53">
         <f t="shared" si="5"/>
         <v>8.8235294117647065E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>63</v>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1913</v>
       </c>
       <c r="B54">
-        <v>1913</v>
+        <v>1613</v>
       </c>
       <c r="C54">
-        <v>1613</v>
+        <v>1589</v>
       </c>
       <c r="D54">
-        <v>1589</v>
+        <v>24</v>
       </c>
       <c r="E54">
-        <v>24</v>
+        <v>681</v>
       </c>
       <c r="F54">
         <v>681</v>
       </c>
       <c r="G54">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="I54">
         <v>626</v>
       </c>
       <c r="J54">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>0.9192364170337739</v>
       </c>
       <c r="L54">
         <v>0.9192364170337739</v>
       </c>
       <c r="M54">
-        <v>0.9192364170337739</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
         <f t="shared" si="3"/>
         <v>0.3880967141971482</v>
       </c>
-      <c r="P54">
+      <c r="O54">
         <f t="shared" si="4"/>
         <v>0.39395846444304594</v>
       </c>
-      <c r="Q54">
+      <c r="P54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>64</v>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>1913</v>
       </c>
       <c r="B55">
-        <v>1913</v>
+        <v>1601</v>
       </c>
       <c r="C55">
-        <v>1601</v>
+        <v>1577</v>
       </c>
       <c r="D55">
-        <v>1577</v>
+        <v>24</v>
       </c>
       <c r="E55">
-        <v>24</v>
+        <v>750</v>
       </c>
       <c r="F55">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G55">
-        <v>749</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>683</v>
       </c>
       <c r="I55">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J55">
-        <v>682</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>0.91066666666666662</v>
       </c>
       <c r="L55">
-        <v>0.91066666666666662</v>
+        <v>0.91054739652870498</v>
       </c>
       <c r="M55">
-        <v>0.91054739652870498</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>1</v>
-      </c>
-      <c r="O55">
         <f t="shared" si="3"/>
         <v>0.42660836976889444</v>
       </c>
-      <c r="P55">
+      <c r="O55">
         <f t="shared" si="4"/>
         <v>0.43246670894102729</v>
       </c>
-      <c r="Q55">
+      <c r="P55">
         <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>66</v>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1913</v>
       </c>
       <c r="B56">
-        <v>1913</v>
+        <v>1627</v>
       </c>
       <c r="C56">
-        <v>1627</v>
+        <v>1602</v>
       </c>
       <c r="D56">
-        <v>1602</v>
+        <v>25</v>
       </c>
       <c r="E56">
-        <v>25</v>
+        <v>629</v>
       </c>
       <c r="F56">
         <v>629</v>
       </c>
       <c r="G56">
-        <v>629</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="I56">
         <v>587</v>
       </c>
       <c r="J56">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>0.93322734499205084</v>
       </c>
       <c r="L56">
         <v>0.93322734499205084</v>
       </c>
       <c r="M56">
-        <v>0.93322734499205084</v>
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
         <f t="shared" si="3"/>
         <v>0.36078672403196066</v>
       </c>
-      <c r="P56">
+      <c r="O56">
         <f t="shared" si="4"/>
         <v>0.36641697877652935</v>
       </c>
-      <c r="Q56">
+      <c r="P56">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>67</v>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>1913</v>
       </c>
       <c r="B57">
-        <v>1913</v>
+        <v>1598</v>
       </c>
       <c r="C57">
-        <v>1598</v>
+        <v>1569</v>
       </c>
       <c r="D57">
-        <v>1569</v>
+        <v>29</v>
       </c>
       <c r="E57">
-        <v>29</v>
+        <v>698</v>
       </c>
       <c r="F57">
         <v>698</v>
       </c>
       <c r="G57">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="I57">
         <v>636</v>
       </c>
       <c r="J57">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>0.91117478510028649</v>
       </c>
       <c r="L57">
         <v>0.91117478510028649</v>
       </c>
       <c r="M57">
-        <v>0.91117478510028649</v>
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
         <f t="shared" si="3"/>
         <v>0.39799749687108887</v>
       </c>
-      <c r="P57">
+      <c r="O57">
         <f t="shared" si="4"/>
         <v>0.40535372848948376</v>
       </c>
-      <c r="Q57">
+      <c r="P57">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>68</v>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>1913</v>
       </c>
       <c r="B58">
-        <v>1913</v>
+        <v>1620</v>
       </c>
       <c r="C58">
-        <v>1620</v>
+        <v>1589</v>
       </c>
       <c r="D58">
-        <v>1589</v>
+        <v>31</v>
       </c>
       <c r="E58">
-        <v>31</v>
+        <v>731</v>
       </c>
       <c r="F58">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G58">
-        <v>729</v>
+        <v>2</v>
       </c>
       <c r="H58">
+        <v>678</v>
+      </c>
+      <c r="I58">
+        <v>676</v>
+      </c>
+      <c r="J58">
         <v>2</v>
       </c>
-      <c r="I58">
-        <v>678</v>
-      </c>
-      <c r="J58">
-        <v>676</v>
-      </c>
       <c r="K58">
-        <v>2</v>
+        <v>0.9274965800273598</v>
       </c>
       <c r="L58">
-        <v>0.9274965800273598</v>
+        <v>0.92729766803840874</v>
       </c>
       <c r="M58">
-        <v>0.92729766803840874</v>
+        <v>1</v>
       </c>
       <c r="N58">
-        <v>1</v>
-      </c>
-      <c r="O58">
         <f t="shared" si="3"/>
         <v>0.41851851851851851</v>
       </c>
-      <c r="P58">
+      <c r="O58">
         <f t="shared" si="4"/>
         <v>0.42542479546884832</v>
       </c>
-      <c r="Q58">
+      <c r="P58">
         <f t="shared" si="5"/>
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>69</v>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>1913</v>
       </c>
       <c r="B59">
-        <v>1913</v>
+        <v>1608</v>
       </c>
       <c r="C59">
-        <v>1608</v>
+        <v>1577</v>
       </c>
       <c r="D59">
-        <v>1577</v>
+        <v>31</v>
       </c>
       <c r="E59">
-        <v>31</v>
+        <v>759</v>
       </c>
       <c r="F59">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G59">
-        <v>758</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>690</v>
       </c>
       <c r="I59">
         <v>690</v>
       </c>
       <c r="J59">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="L59">
-        <v>0.90909090909090906</v>
+        <v>0.91029023746701843</v>
       </c>
       <c r="M59">
-        <v>0.91029023746701843</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
         <f t="shared" si="3"/>
         <v>0.42910447761194032</v>
       </c>
-      <c r="P59">
+      <c r="O59">
         <f t="shared" si="4"/>
         <v>0.4375396322130628</v>
       </c>
-      <c r="Q59">
+      <c r="P59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>70</v>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>1913</v>
       </c>
       <c r="B60">
-        <v>1913</v>
+        <v>1602</v>
       </c>
       <c r="C60">
-        <v>1602</v>
+        <v>1565</v>
       </c>
       <c r="D60">
-        <v>1565</v>
+        <v>37</v>
       </c>
       <c r="E60">
-        <v>37</v>
+        <v>742</v>
       </c>
       <c r="F60">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="G60">
-        <v>739</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>683</v>
       </c>
       <c r="I60">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J60">
-        <v>681</v>
+        <v>2</v>
       </c>
       <c r="K60">
-        <v>2</v>
+        <v>0.92048517520215634</v>
       </c>
       <c r="L60">
-        <v>0.92048517520215634</v>
+        <v>0.92151556156968872</v>
       </c>
       <c r="M60">
-        <v>0.92151556156968872</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N60">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O60">
         <f t="shared" si="3"/>
         <v>0.42634207240948813</v>
       </c>
-      <c r="P60">
+      <c r="O60">
         <f t="shared" si="4"/>
         <v>0.4351437699680511</v>
       </c>
-      <c r="Q60">
+      <c r="P60">
         <f t="shared" si="5"/>
         <v>5.4054054054054057E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>71</v>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>1913</v>
       </c>
       <c r="B61">
-        <v>1913</v>
+        <v>1628</v>
       </c>
       <c r="C61">
-        <v>1628</v>
+        <v>1622</v>
       </c>
       <c r="D61">
-        <v>1622</v>
+        <v>6</v>
       </c>
       <c r="E61">
-        <v>6</v>
+        <v>660</v>
       </c>
       <c r="F61">
         <v>660</v>
       </c>
       <c r="G61">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="I61">
         <v>607</v>
       </c>
       <c r="J61">
-        <v>607</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>0.91969696969696968</v>
       </c>
       <c r="L61">
         <v>0.91969696969696968</v>
       </c>
       <c r="M61">
-        <v>0.91969696969696968</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
         <f t="shared" si="3"/>
         <v>0.37285012285012287</v>
       </c>
-      <c r="P61">
+      <c r="O61">
         <f t="shared" si="4"/>
         <v>0.37422934648581996</v>
       </c>
-      <c r="Q61">
+      <c r="P61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>72</v>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>1913</v>
       </c>
       <c r="B62">
-        <v>1913</v>
+        <v>1619</v>
       </c>
       <c r="C62">
-        <v>1619</v>
+        <v>1597</v>
       </c>
       <c r="D62">
-        <v>1597</v>
+        <v>22</v>
       </c>
       <c r="E62">
-        <v>22</v>
+        <v>691</v>
       </c>
       <c r="F62">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G62">
-        <v>690</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>641</v>
       </c>
       <c r="I62">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J62">
-        <v>640</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>1</v>
+        <v>0.9276410998552822</v>
       </c>
       <c r="L62">
-        <v>0.9276410998552822</v>
+        <v>0.92753623188405798</v>
       </c>
       <c r="M62">
-        <v>0.92753623188405798</v>
+        <v>1</v>
       </c>
       <c r="N62">
-        <v>1</v>
-      </c>
-      <c r="O62">
         <f t="shared" si="3"/>
         <v>0.39592340951204447</v>
       </c>
-      <c r="P62">
+      <c r="O62">
         <f t="shared" si="4"/>
         <v>0.40075140889167188</v>
       </c>
-      <c r="Q62">
+      <c r="P62">
         <f t="shared" si="5"/>
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>73</v>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1913</v>
       </c>
       <c r="B63">
-        <v>1913</v>
+        <v>1621</v>
       </c>
       <c r="C63">
-        <v>1621</v>
+        <v>1593</v>
       </c>
       <c r="D63">
-        <v>1593</v>
+        <v>28</v>
       </c>
       <c r="E63">
-        <v>28</v>
+        <v>717</v>
       </c>
       <c r="F63">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G63">
-        <v>715</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>653</v>
       </c>
       <c r="I63">
         <v>653</v>
       </c>
       <c r="J63">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>0.9107391910739191</v>
       </c>
       <c r="L63">
-        <v>0.9107391910739191</v>
+        <v>0.91328671328671329</v>
       </c>
       <c r="M63">
-        <v>0.91328671328671329</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
         <f t="shared" si="3"/>
         <v>0.40283775447254783</v>
       </c>
-      <c r="P63">
+      <c r="O63">
         <f t="shared" si="4"/>
         <v>0.40991839296924043</v>
       </c>
-      <c r="Q63">
+      <c r="P63">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>74</v>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1913</v>
       </c>
       <c r="B64">
-        <v>1913</v>
+        <v>1613</v>
       </c>
       <c r="C64">
-        <v>1613</v>
+        <v>1600</v>
       </c>
       <c r="D64">
-        <v>1600</v>
+        <v>13</v>
       </c>
       <c r="E64">
-        <v>13</v>
+        <v>692</v>
       </c>
       <c r="F64">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G64">
-        <v>691</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>647</v>
       </c>
       <c r="I64">
         <v>647</v>
       </c>
       <c r="J64">
-        <v>647</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>0.93497109826589597</v>
       </c>
       <c r="L64">
-        <v>0.93497109826589597</v>
+        <v>0.93632416787264838</v>
       </c>
       <c r="M64">
-        <v>0.93632416787264838</v>
+        <v>0</v>
       </c>
       <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
         <f t="shared" si="3"/>
         <v>0.40111593304401738</v>
       </c>
-      <c r="P64">
+      <c r="O64">
         <f t="shared" si="4"/>
         <v>0.40437499999999998</v>
       </c>
-      <c r="Q64">
+      <c r="P64">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>76</v>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1913</v>
       </c>
       <c r="B65">
-        <v>1913</v>
+        <v>1614</v>
       </c>
       <c r="C65">
-        <v>1614</v>
+        <v>1601</v>
       </c>
       <c r="D65">
-        <v>1601</v>
+        <v>13</v>
       </c>
       <c r="E65">
-        <v>13</v>
+        <v>724</v>
       </c>
       <c r="F65">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G65">
-        <v>720</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>662</v>
       </c>
       <c r="I65">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J65">
-        <v>661</v>
+        <v>1</v>
       </c>
       <c r="K65">
-        <v>1</v>
+        <v>0.91436464088397795</v>
       </c>
       <c r="L65">
-        <v>0.91436464088397795</v>
+        <v>0.91805555555555551</v>
       </c>
       <c r="M65">
-        <v>0.91805555555555551</v>
+        <v>0.25</v>
       </c>
       <c r="N65">
-        <v>0.25</v>
-      </c>
-      <c r="O65">
         <f t="shared" si="3"/>
         <v>0.41016109045848825</v>
       </c>
-      <c r="P65">
+      <c r="O65">
         <f t="shared" si="4"/>
         <v>0.41286695815115554</v>
       </c>
-      <c r="Q65">
+      <c r="P65">
         <f t="shared" si="5"/>
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>77</v>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1913</v>
       </c>
       <c r="B66">
-        <v>1913</v>
+        <v>1630</v>
       </c>
       <c r="C66">
-        <v>1630</v>
+        <v>1605</v>
       </c>
       <c r="D66">
-        <v>1605</v>
+        <v>25</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>701</v>
       </c>
       <c r="F66">
         <v>701</v>
       </c>
       <c r="G66">
-        <v>701</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="I66">
         <v>654</v>
       </c>
       <c r="J66">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>0.93295292439372324</v>
       </c>
       <c r="L66">
         <v>0.93295292439372324</v>
       </c>
       <c r="M66">
-        <v>0.93295292439372324</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
         <f t="shared" si="3"/>
         <v>0.40122699386503069</v>
       </c>
-      <c r="P66">
+      <c r="O66">
         <f t="shared" si="4"/>
         <v>0.40747663551401869</v>
       </c>
-      <c r="Q66">
+      <c r="P66">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>78</v>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1913</v>
       </c>
       <c r="B67">
-        <v>1913</v>
+        <v>1625</v>
       </c>
       <c r="C67">
-        <v>1625</v>
+        <v>1591</v>
       </c>
       <c r="D67">
-        <v>1591</v>
+        <v>34</v>
       </c>
       <c r="E67">
-        <v>34</v>
+        <v>711</v>
       </c>
       <c r="F67">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G67">
-        <v>709</v>
+        <v>2</v>
       </c>
       <c r="H67">
+        <v>646</v>
+      </c>
+      <c r="I67">
+        <v>644</v>
+      </c>
+      <c r="J67">
         <v>2</v>
       </c>
-      <c r="I67">
-        <v>646</v>
-      </c>
-      <c r="J67">
-        <v>644</v>
-      </c>
       <c r="K67">
-        <v>2</v>
+        <v>0.90857946554149083</v>
       </c>
       <c r="L67">
-        <v>0.90857946554149083</v>
+        <v>0.90832157968970384</v>
       </c>
       <c r="M67">
-        <v>0.90832157968970384</v>
+        <v>1</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <f t="shared" ref="N67:N98" si="6">H67/B67</f>
+        <v>0.39753846153846156</v>
       </c>
       <c r="O67">
-        <f t="shared" ref="O67:O98" si="6">I67/C67</f>
-        <v>0.39753846153846156</v>
+        <f t="shared" ref="O67:O98" si="7">I67/C67</f>
+        <v>0.40477686989314898</v>
       </c>
       <c r="P67">
-        <f t="shared" ref="P67:P98" si="7">J67/D67</f>
-        <v>0.40477686989314898</v>
-      </c>
-      <c r="Q67">
-        <f t="shared" ref="Q67:Q98" si="8">K67/E67</f>
+        <f t="shared" ref="P67:P98" si="8">J67/D67</f>
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>79</v>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1913</v>
       </c>
       <c r="B68">
-        <v>1913</v>
+        <v>1624</v>
       </c>
       <c r="C68">
-        <v>1624</v>
+        <v>1600</v>
       </c>
       <c r="D68">
-        <v>1600</v>
+        <v>24</v>
       </c>
       <c r="E68">
-        <v>24</v>
+        <v>667</v>
       </c>
       <c r="F68">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G68">
-        <v>666</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>627</v>
       </c>
       <c r="I68">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J68">
-        <v>626</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>1</v>
+        <v>0.94002998500749624</v>
       </c>
       <c r="L68">
-        <v>0.94002998500749624</v>
+        <v>0.93993993993993996</v>
       </c>
       <c r="M68">
-        <v>0.93993993993993996</v>
+        <v>1</v>
       </c>
       <c r="N68">
-        <v>1</v>
-      </c>
-      <c r="O68">
         <f t="shared" si="6"/>
         <v>0.38608374384236455</v>
       </c>
-      <c r="P68">
+      <c r="O68">
         <f t="shared" si="7"/>
         <v>0.39124999999999999</v>
       </c>
-      <c r="Q68">
+      <c r="P68">
         <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>80</v>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1913</v>
       </c>
       <c r="B69">
-        <v>1913</v>
+        <v>1589</v>
       </c>
       <c r="C69">
-        <v>1589</v>
+        <v>1560</v>
       </c>
       <c r="D69">
-        <v>1560</v>
+        <v>29</v>
       </c>
       <c r="E69">
-        <v>29</v>
+        <v>720</v>
       </c>
       <c r="F69">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G69">
-        <v>719</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>668</v>
       </c>
       <c r="I69">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J69">
-        <v>667</v>
+        <v>1</v>
       </c>
       <c r="K69">
-        <v>1</v>
+        <v>0.92777777777777781</v>
       </c>
       <c r="L69">
-        <v>0.92777777777777781</v>
+        <v>0.92767732962447846</v>
       </c>
       <c r="M69">
-        <v>0.92767732962447846</v>
+        <v>1</v>
       </c>
       <c r="N69">
-        <v>1</v>
-      </c>
-      <c r="O69">
         <f t="shared" si="6"/>
         <v>0.42039018250471993</v>
       </c>
-      <c r="P69">
+      <c r="O69">
         <f t="shared" si="7"/>
         <v>0.42756410256410254</v>
       </c>
-      <c r="Q69">
+      <c r="P69">
         <f t="shared" si="8"/>
         <v>3.4482758620689655E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>82</v>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>1913</v>
       </c>
       <c r="B70">
-        <v>1913</v>
+        <v>1613</v>
       </c>
       <c r="C70">
-        <v>1613</v>
+        <v>1583</v>
       </c>
       <c r="D70">
-        <v>1583</v>
+        <v>30</v>
       </c>
       <c r="E70">
-        <v>30</v>
+        <v>676</v>
       </c>
       <c r="F70">
         <v>676</v>
       </c>
       <c r="G70">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="I70">
         <v>623</v>
       </c>
       <c r="J70">
-        <v>623</v>
+        <v>0</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>0.92159763313609466</v>
       </c>
       <c r="L70">
         <v>0.92159763313609466</v>
       </c>
       <c r="M70">
-        <v>0.92159763313609466</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
         <f t="shared" si="6"/>
         <v>0.3862368257904526</v>
       </c>
-      <c r="P70">
+      <c r="O70">
         <f t="shared" si="7"/>
         <v>0.39355653821857234</v>
       </c>
-      <c r="Q70">
+      <c r="P70">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>83</v>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1913</v>
       </c>
       <c r="B71">
-        <v>1913</v>
+        <v>1622</v>
       </c>
       <c r="C71">
-        <v>1622</v>
+        <v>1608</v>
       </c>
       <c r="D71">
-        <v>1608</v>
+        <v>14</v>
       </c>
       <c r="E71">
-        <v>14</v>
+        <v>652</v>
       </c>
       <c r="F71">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G71">
-        <v>650</v>
+        <v>2</v>
       </c>
       <c r="H71">
+        <v>610</v>
+      </c>
+      <c r="I71">
+        <v>608</v>
+      </c>
+      <c r="J71">
         <v>2</v>
       </c>
-      <c r="I71">
-        <v>610</v>
-      </c>
-      <c r="J71">
-        <v>608</v>
-      </c>
       <c r="K71">
-        <v>2</v>
+        <v>0.93558282208588961</v>
       </c>
       <c r="L71">
-        <v>0.93558282208588961</v>
+        <v>0.93538461538461537</v>
       </c>
       <c r="M71">
-        <v>0.93538461538461537</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>1</v>
-      </c>
-      <c r="O71">
         <f t="shared" si="6"/>
         <v>0.37607891491985201</v>
       </c>
-      <c r="P71">
+      <c r="O71">
         <f t="shared" si="7"/>
         <v>0.37810945273631841</v>
       </c>
-      <c r="Q71">
+      <c r="P71">
         <f t="shared" si="8"/>
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>85</v>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>1913</v>
       </c>
       <c r="B72">
-        <v>1913</v>
+        <v>1609</v>
       </c>
       <c r="C72">
-        <v>1609</v>
+        <v>1583</v>
       </c>
       <c r="D72">
-        <v>1583</v>
+        <v>26</v>
       </c>
       <c r="E72">
-        <v>26</v>
+        <v>702</v>
       </c>
       <c r="F72">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G72">
-        <v>701</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>647</v>
       </c>
       <c r="I72">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J72">
-        <v>646</v>
+        <v>1</v>
       </c>
       <c r="K72">
-        <v>1</v>
+        <v>0.92165242165242167</v>
       </c>
       <c r="L72">
-        <v>0.92165242165242167</v>
+        <v>0.92154065620542081</v>
       </c>
       <c r="M72">
-        <v>0.92154065620542081</v>
+        <v>1</v>
       </c>
       <c r="N72">
-        <v>1</v>
-      </c>
-      <c r="O72">
         <f t="shared" si="6"/>
         <v>0.40211311373523928</v>
       </c>
-      <c r="P72">
+      <c r="O72">
         <f t="shared" si="7"/>
         <v>0.40808591282375239</v>
       </c>
-      <c r="Q72">
+      <c r="P72">
         <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>86</v>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>1913</v>
       </c>
       <c r="B73">
-        <v>1913</v>
+        <v>1628</v>
       </c>
       <c r="C73">
-        <v>1628</v>
+        <v>1601</v>
       </c>
       <c r="D73">
-        <v>1601</v>
+        <v>27</v>
       </c>
       <c r="E73">
-        <v>27</v>
+        <v>688</v>
       </c>
       <c r="F73">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G73">
-        <v>687</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>640</v>
       </c>
       <c r="I73">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J73">
-        <v>639</v>
+        <v>1</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="L73">
-        <v>0.93023255813953487</v>
+        <v>0.93013100436681218</v>
       </c>
       <c r="M73">
-        <v>0.93013100436681218</v>
+        <v>1</v>
       </c>
       <c r="N73">
-        <v>1</v>
-      </c>
-      <c r="O73">
         <f t="shared" si="6"/>
         <v>0.3931203931203931</v>
       </c>
-      <c r="P73">
+      <c r="O73">
         <f t="shared" si="7"/>
         <v>0.39912554653341664</v>
       </c>
-      <c r="Q73">
+      <c r="P73">
         <f t="shared" si="8"/>
         <v>3.7037037037037035E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>87</v>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1913</v>
       </c>
       <c r="B74">
-        <v>1913</v>
+        <v>1627</v>
       </c>
       <c r="C74">
-        <v>1627</v>
+        <v>1592</v>
       </c>
       <c r="D74">
-        <v>1592</v>
+        <v>35</v>
       </c>
       <c r="E74">
-        <v>35</v>
+        <v>653</v>
       </c>
       <c r="F74">
         <v>653</v>
       </c>
       <c r="G74">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="I74">
         <v>614</v>
       </c>
       <c r="J74">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>0.9402756508422665</v>
       </c>
       <c r="L74">
         <v>0.9402756508422665</v>
       </c>
       <c r="M74">
-        <v>0.9402756508422665</v>
+        <v>0</v>
       </c>
       <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
         <f t="shared" si="6"/>
         <v>0.37738168408113093</v>
       </c>
-      <c r="P74">
+      <c r="O74">
         <f t="shared" si="7"/>
         <v>0.38567839195979897</v>
       </c>
-      <c r="Q74">
+      <c r="P74">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>88</v>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>1913</v>
       </c>
       <c r="B75">
-        <v>1913</v>
+        <v>1614</v>
       </c>
       <c r="C75">
-        <v>1614</v>
+        <v>1584</v>
       </c>
       <c r="D75">
-        <v>1584</v>
+        <v>30</v>
       </c>
       <c r="E75">
-        <v>30</v>
+        <v>728</v>
       </c>
       <c r="F75">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G75">
-        <v>726</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>679</v>
       </c>
       <c r="I75">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J75">
-        <v>678</v>
+        <v>1</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>0.93269230769230771</v>
       </c>
       <c r="L75">
-        <v>0.93269230769230771</v>
+        <v>0.93388429752066116</v>
       </c>
       <c r="M75">
-        <v>0.93388429752066116</v>
+        <v>0.5</v>
       </c>
       <c r="N75">
-        <v>0.5</v>
-      </c>
-      <c r="O75">
         <f t="shared" si="6"/>
         <v>0.42069392812887235</v>
       </c>
-      <c r="P75">
+      <c r="O75">
         <f t="shared" si="7"/>
         <v>0.42803030303030304</v>
       </c>
-      <c r="Q75">
+      <c r="P75">
         <f t="shared" si="8"/>
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>89</v>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>1913</v>
       </c>
       <c r="B76">
-        <v>1913</v>
+        <v>1618</v>
       </c>
       <c r="C76">
-        <v>1618</v>
+        <v>1592</v>
       </c>
       <c r="D76">
-        <v>1592</v>
+        <v>26</v>
       </c>
       <c r="E76">
-        <v>26</v>
+        <v>687</v>
       </c>
       <c r="F76">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G76">
-        <v>686</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>649</v>
       </c>
       <c r="I76">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J76">
-        <v>648</v>
+        <v>1</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>0.94468704512372637</v>
       </c>
       <c r="L76">
-        <v>0.94468704512372637</v>
+        <v>0.94460641399416911</v>
       </c>
       <c r="M76">
-        <v>0.94460641399416911</v>
+        <v>1</v>
       </c>
       <c r="N76">
-        <v>1</v>
-      </c>
-      <c r="O76">
         <f t="shared" si="6"/>
         <v>0.4011124845488257</v>
       </c>
-      <c r="P76">
+      <c r="O76">
         <f t="shared" si="7"/>
         <v>0.40703517587939697</v>
       </c>
-      <c r="Q76">
+      <c r="P76">
         <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>91</v>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>1913</v>
       </c>
       <c r="B77">
-        <v>1913</v>
+        <v>1635</v>
       </c>
       <c r="C77">
-        <v>1635</v>
+        <v>1591</v>
       </c>
       <c r="D77">
-        <v>1591</v>
+        <v>44</v>
       </c>
       <c r="E77">
-        <v>44</v>
+        <v>683</v>
       </c>
       <c r="F77">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G77">
-        <v>682</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>639</v>
       </c>
       <c r="I77">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J77">
-        <v>638</v>
+        <v>1</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>0.93557833089311859</v>
       </c>
       <c r="L77">
-        <v>0.93557833089311859</v>
+        <v>0.93548387096774188</v>
       </c>
       <c r="M77">
-        <v>0.93548387096774188</v>
+        <v>1</v>
       </c>
       <c r="N77">
-        <v>1</v>
-      </c>
-      <c r="O77">
         <f t="shared" si="6"/>
         <v>0.39082568807339452</v>
       </c>
-      <c r="P77">
+      <c r="O77">
         <f t="shared" si="7"/>
         <v>0.40100565681961031</v>
       </c>
-      <c r="Q77">
+      <c r="P77">
         <f t="shared" si="8"/>
         <v>2.2727272727272728E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>92</v>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>1913</v>
       </c>
       <c r="B78">
-        <v>1913</v>
+        <v>1594</v>
       </c>
       <c r="C78">
-        <v>1594</v>
+        <v>1565</v>
       </c>
       <c r="D78">
-        <v>1565</v>
+        <v>29</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>704</v>
       </c>
       <c r="F78">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G78">
-        <v>703</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>641</v>
       </c>
       <c r="I78">
         <v>641</v>
       </c>
       <c r="J78">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>0.91051136363636365</v>
       </c>
       <c r="L78">
-        <v>0.91051136363636365</v>
+        <v>0.91180654338549072</v>
       </c>
       <c r="M78">
-        <v>0.91180654338549072</v>
+        <v>0</v>
       </c>
       <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
         <f t="shared" si="6"/>
         <v>0.40213299874529485</v>
       </c>
-      <c r="P78">
+      <c r="O78">
         <f t="shared" si="7"/>
         <v>0.40958466453674119</v>
       </c>
-      <c r="Q78">
+      <c r="P78">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>93</v>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>1913</v>
       </c>
       <c r="B79">
-        <v>1913</v>
+        <v>1607</v>
       </c>
       <c r="C79">
-        <v>1607</v>
+        <v>1581</v>
       </c>
       <c r="D79">
-        <v>1581</v>
+        <v>26</v>
       </c>
       <c r="E79">
-        <v>26</v>
+        <v>677</v>
       </c>
       <c r="F79">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G79">
-        <v>676</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>623</v>
       </c>
       <c r="I79">
         <v>623</v>
       </c>
       <c r="J79">
-        <v>623</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>0.92023633677991135</v>
       </c>
       <c r="L79">
-        <v>0.92023633677991135</v>
+        <v>0.92159763313609466</v>
       </c>
       <c r="M79">
-        <v>0.92159763313609466</v>
+        <v>0</v>
       </c>
       <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
         <f t="shared" si="6"/>
         <v>0.38767890479153705</v>
       </c>
-      <c r="P79">
+      <c r="O79">
         <f t="shared" si="7"/>
         <v>0.39405439595192915</v>
       </c>
-      <c r="Q79">
+      <c r="P79">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>95</v>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>1913</v>
       </c>
       <c r="B80">
-        <v>1913</v>
+        <v>1599</v>
       </c>
       <c r="C80">
-        <v>1599</v>
+        <v>1577</v>
       </c>
       <c r="D80">
-        <v>1577</v>
+        <v>22</v>
       </c>
       <c r="E80">
-        <v>22</v>
+        <v>719</v>
       </c>
       <c r="F80">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G80">
-        <v>718</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>666</v>
       </c>
       <c r="I80">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J80">
-        <v>665</v>
+        <v>1</v>
       </c>
       <c r="K80">
-        <v>1</v>
+        <v>0.92628650904033383</v>
       </c>
       <c r="L80">
-        <v>0.92628650904033383</v>
+        <v>0.92618384401114207</v>
       </c>
       <c r="M80">
-        <v>0.92618384401114207</v>
+        <v>1</v>
       </c>
       <c r="N80">
-        <v>1</v>
-      </c>
-      <c r="O80">
         <f t="shared" si="6"/>
         <v>0.41651031894934332</v>
       </c>
-      <c r="P80">
+      <c r="O80">
         <f t="shared" si="7"/>
         <v>0.42168674698795183</v>
       </c>
-      <c r="Q80">
+      <c r="P80">
         <f t="shared" si="8"/>
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>96</v>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>1913</v>
       </c>
       <c r="B81">
-        <v>1913</v>
+        <v>1626</v>
       </c>
       <c r="C81">
-        <v>1626</v>
+        <v>1599</v>
       </c>
       <c r="D81">
-        <v>1599</v>
+        <v>27</v>
       </c>
       <c r="E81">
-        <v>27</v>
+        <v>700</v>
       </c>
       <c r="F81">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G81">
-        <v>697</v>
+        <v>3</v>
       </c>
       <c r="H81">
-        <v>3</v>
+        <v>652</v>
       </c>
       <c r="I81">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="J81">
-        <v>650</v>
+        <v>2</v>
       </c>
       <c r="K81">
-        <v>2</v>
+        <v>0.93142857142857138</v>
       </c>
       <c r="L81">
-        <v>0.93142857142857138</v>
+        <v>0.93256814921090392</v>
       </c>
       <c r="M81">
-        <v>0.93256814921090392</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N81">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O81">
         <f t="shared" si="6"/>
         <v>0.40098400984009841</v>
       </c>
-      <c r="P81">
+      <c r="O81">
         <f t="shared" si="7"/>
         <v>0.4065040650406504</v>
       </c>
-      <c r="Q81">
+      <c r="P81">
         <f t="shared" si="8"/>
         <v>7.407407407407407E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>97</v>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>1913</v>
       </c>
       <c r="B82">
-        <v>1913</v>
+        <v>1615</v>
       </c>
       <c r="C82">
-        <v>1615</v>
+        <v>1588</v>
       </c>
       <c r="D82">
-        <v>1588</v>
+        <v>27</v>
       </c>
       <c r="E82">
-        <v>27</v>
+        <v>687</v>
       </c>
       <c r="F82">
         <v>687</v>
       </c>
       <c r="G82">
-        <v>687</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="I82">
         <v>639</v>
       </c>
       <c r="J82">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>0.93013100436681218</v>
       </c>
       <c r="L82">
         <v>0.93013100436681218</v>
       </c>
       <c r="M82">
-        <v>0.93013100436681218</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
         <f t="shared" si="6"/>
         <v>0.39566563467492261</v>
       </c>
-      <c r="P82">
+      <c r="O82">
         <f t="shared" si="7"/>
         <v>0.40239294710327456</v>
       </c>
-      <c r="Q82">
+      <c r="P82">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>98</v>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>1913</v>
       </c>
       <c r="B83">
-        <v>1913</v>
+        <v>1603</v>
       </c>
       <c r="C83">
-        <v>1603</v>
+        <v>1578</v>
       </c>
       <c r="D83">
-        <v>1578</v>
+        <v>25</v>
       </c>
       <c r="E83">
-        <v>25</v>
+        <v>713</v>
       </c>
       <c r="F83">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G83">
-        <v>711</v>
+        <v>2</v>
       </c>
       <c r="H83">
+        <v>663</v>
+      </c>
+      <c r="I83">
+        <v>661</v>
+      </c>
+      <c r="J83">
         <v>2</v>
       </c>
-      <c r="I83">
-        <v>663</v>
-      </c>
-      <c r="J83">
-        <v>661</v>
-      </c>
       <c r="K83">
-        <v>2</v>
+        <v>0.92987377279102379</v>
       </c>
       <c r="L83">
-        <v>0.92987377279102379</v>
+        <v>0.92967651195499301</v>
       </c>
       <c r="M83">
-        <v>0.92967651195499301</v>
+        <v>1</v>
       </c>
       <c r="N83">
-        <v>1</v>
-      </c>
-      <c r="O83">
         <f t="shared" si="6"/>
         <v>0.41359950093574549</v>
       </c>
-      <c r="P83">
+      <c r="O83">
         <f t="shared" si="7"/>
         <v>0.41888466413181241</v>
       </c>
-      <c r="Q83">
+      <c r="P83">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>99</v>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>1913</v>
       </c>
       <c r="B84">
-        <v>1913</v>
+        <v>1625</v>
       </c>
       <c r="C84">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="D84">
-        <v>1600</v>
+        <v>25</v>
       </c>
       <c r="E84">
-        <v>25</v>
+        <v>698</v>
       </c>
       <c r="F84">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G84">
-        <v>695</v>
+        <v>3</v>
       </c>
       <c r="H84">
-        <v>3</v>
+        <v>646</v>
       </c>
       <c r="I84">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J84">
-        <v>645</v>
+        <v>1</v>
       </c>
       <c r="K84">
-        <v>1</v>
+        <v>0.92550143266475648</v>
       </c>
       <c r="L84">
-        <v>0.92550143266475648</v>
+        <v>0.92805755395683454</v>
       </c>
       <c r="M84">
-        <v>0.92805755395683454</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N84">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="O84">
         <f t="shared" si="6"/>
         <v>0.39753846153846156</v>
       </c>
-      <c r="P84">
+      <c r="O84">
         <f t="shared" si="7"/>
         <v>0.40312500000000001</v>
       </c>
-      <c r="Q84">
+      <c r="P84">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>100</v>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>1913</v>
       </c>
       <c r="B85">
-        <v>1913</v>
+        <v>1617</v>
       </c>
       <c r="C85">
-        <v>1617</v>
+        <v>1595</v>
       </c>
       <c r="D85">
-        <v>1595</v>
+        <v>22</v>
       </c>
       <c r="E85">
-        <v>22</v>
+        <v>721</v>
       </c>
       <c r="F85">
         <v>721</v>
       </c>
       <c r="G85">
-        <v>721</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="I85">
         <v>661</v>
       </c>
       <c r="J85">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>0.91678224687933429</v>
       </c>
       <c r="L85">
         <v>0.91678224687933429</v>
       </c>
       <c r="M85">
-        <v>0.91678224687933429</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
         <f t="shared" si="6"/>
         <v>0.40878169449598023</v>
       </c>
-      <c r="P85">
+      <c r="O85">
         <f t="shared" si="7"/>
         <v>0.41442006269592474</v>
       </c>
-      <c r="Q85">
+      <c r="P85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>101</v>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>1913</v>
       </c>
       <c r="B86">
-        <v>1913</v>
+        <v>1616</v>
       </c>
       <c r="C86">
-        <v>1616</v>
+        <v>1587</v>
       </c>
       <c r="D86">
-        <v>1587</v>
+        <v>29</v>
       </c>
       <c r="E86">
-        <v>29</v>
+        <v>661</v>
       </c>
       <c r="F86">
         <v>661</v>
       </c>
       <c r="G86">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="I86">
         <v>615</v>
       </c>
       <c r="J86">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>0.93040847201210286</v>
       </c>
       <c r="L86">
         <v>0.93040847201210286</v>
       </c>
       <c r="M86">
-        <v>0.93040847201210286</v>
+        <v>0</v>
       </c>
       <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
         <f t="shared" si="6"/>
         <v>0.38056930693069307</v>
       </c>
-      <c r="P86">
+      <c r="O86">
         <f t="shared" si="7"/>
         <v>0.38752362948960301</v>
       </c>
-      <c r="Q86">
+      <c r="P86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>102</v>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1913</v>
       </c>
       <c r="B87">
-        <v>1913</v>
+        <v>1603</v>
       </c>
       <c r="C87">
-        <v>1603</v>
+        <v>1575</v>
       </c>
       <c r="D87">
-        <v>1575</v>
+        <v>28</v>
       </c>
       <c r="E87">
-        <v>28</v>
+        <v>695</v>
       </c>
       <c r="F87">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G87">
-        <v>694</v>
+        <v>1</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>637</v>
       </c>
       <c r="I87">
         <v>637</v>
       </c>
       <c r="J87">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>0.91654676258992807</v>
       </c>
       <c r="L87">
-        <v>0.91654676258992807</v>
+        <v>0.91786743515850144</v>
       </c>
       <c r="M87">
-        <v>0.91786743515850144</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
         <f t="shared" si="6"/>
         <v>0.39737991266375544</v>
       </c>
-      <c r="P87">
+      <c r="O87">
         <f t="shared" si="7"/>
         <v>0.40444444444444444</v>
       </c>
-      <c r="Q87">
+      <c r="P87">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>103</v>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1913</v>
       </c>
       <c r="B88">
-        <v>1913</v>
+        <v>1608</v>
       </c>
       <c r="C88">
-        <v>1608</v>
+        <v>1570</v>
       </c>
       <c r="D88">
-        <v>1570</v>
+        <v>38</v>
       </c>
       <c r="E88">
-        <v>38</v>
+        <v>700</v>
       </c>
       <c r="F88">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G88">
-        <v>699</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>650</v>
       </c>
       <c r="I88">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J88">
-        <v>649</v>
+        <v>1</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="L88">
-        <v>0.9285714285714286</v>
+        <v>0.92846924177396284</v>
       </c>
       <c r="M88">
-        <v>0.92846924177396284</v>
+        <v>1</v>
       </c>
       <c r="N88">
-        <v>1</v>
-      </c>
-      <c r="O88">
         <f t="shared" si="6"/>
         <v>0.40422885572139305</v>
       </c>
-      <c r="P88">
+      <c r="O88">
         <f t="shared" si="7"/>
         <v>0.41337579617834397</v>
       </c>
-      <c r="Q88">
+      <c r="P88">
         <f t="shared" si="8"/>
         <v>2.6315789473684209E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>104</v>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1913</v>
       </c>
       <c r="B89">
-        <v>1913</v>
+        <v>1626</v>
       </c>
       <c r="C89">
-        <v>1626</v>
+        <v>1602</v>
       </c>
       <c r="D89">
-        <v>1602</v>
+        <v>24</v>
       </c>
       <c r="E89">
-        <v>24</v>
+        <v>661</v>
       </c>
       <c r="F89">
         <v>661</v>
       </c>
       <c r="G89">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="I89">
         <v>623</v>
       </c>
       <c r="J89">
-        <v>623</v>
+        <v>0</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>0.94251134644478063</v>
       </c>
       <c r="L89">
         <v>0.94251134644478063</v>
       </c>
       <c r="M89">
-        <v>0.94251134644478063</v>
+        <v>0</v>
       </c>
       <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
         <f t="shared" si="6"/>
         <v>0.38314883148831486</v>
       </c>
-      <c r="P89">
+      <c r="O89">
         <f t="shared" si="7"/>
         <v>0.3888888888888889</v>
       </c>
-      <c r="Q89">
+      <c r="P89">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>105</v>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1913</v>
       </c>
       <c r="B90">
-        <v>1913</v>
+        <v>1627</v>
       </c>
       <c r="C90">
-        <v>1627</v>
+        <v>1600</v>
       </c>
       <c r="D90">
-        <v>1600</v>
+        <v>27</v>
       </c>
       <c r="E90">
-        <v>27</v>
+        <v>641</v>
       </c>
       <c r="F90">
         <v>641</v>
       </c>
       <c r="G90">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="I90">
         <v>591</v>
       </c>
       <c r="J90">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>0.92199687987519496</v>
       </c>
       <c r="L90">
         <v>0.92199687987519496</v>
       </c>
       <c r="M90">
-        <v>0.92199687987519496</v>
+        <v>0</v>
       </c>
       <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
         <f t="shared" si="6"/>
         <v>0.36324523663183772</v>
       </c>
-      <c r="P90">
+      <c r="O90">
         <f t="shared" si="7"/>
         <v>0.36937500000000001</v>
       </c>
-      <c r="Q90">
+      <c r="P90">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>106</v>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1913</v>
       </c>
       <c r="B91">
-        <v>1913</v>
+        <v>1630</v>
       </c>
       <c r="C91">
-        <v>1630</v>
+        <v>1603</v>
       </c>
       <c r="D91">
-        <v>1603</v>
+        <v>27</v>
       </c>
       <c r="E91">
-        <v>27</v>
+        <v>660</v>
       </c>
       <c r="F91">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G91">
-        <v>659</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>610</v>
       </c>
       <c r="I91">
         <v>610</v>
       </c>
       <c r="J91">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>0.9242424242424242</v>
       </c>
       <c r="L91">
-        <v>0.9242424242424242</v>
+        <v>0.92564491654021241</v>
       </c>
       <c r="M91">
-        <v>0.92564491654021241</v>
+        <v>0</v>
       </c>
       <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
         <f t="shared" si="6"/>
         <v>0.37423312883435583</v>
       </c>
-      <c r="P91">
+      <c r="O91">
         <f t="shared" si="7"/>
         <v>0.38053649407361195</v>
       </c>
-      <c r="Q91">
+      <c r="P91">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>109</v>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1913</v>
       </c>
       <c r="B92">
-        <v>1913</v>
+        <v>1633</v>
       </c>
       <c r="C92">
-        <v>1633</v>
+        <v>1605</v>
       </c>
       <c r="D92">
-        <v>1605</v>
+        <v>28</v>
       </c>
       <c r="E92">
-        <v>28</v>
+        <v>692</v>
       </c>
       <c r="F92">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G92">
-        <v>690</v>
+        <v>2</v>
       </c>
       <c r="H92">
-        <v>2</v>
+        <v>641</v>
       </c>
       <c r="I92">
         <v>641</v>
       </c>
       <c r="J92">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>0.92630057803468213</v>
       </c>
       <c r="L92">
-        <v>0.92630057803468213</v>
+        <v>0.92898550724637685</v>
       </c>
       <c r="M92">
-        <v>0.92898550724637685</v>
+        <v>0</v>
       </c>
       <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
         <f t="shared" si="6"/>
         <v>0.3925290875688916</v>
       </c>
-      <c r="P92">
+      <c r="O92">
         <f t="shared" si="7"/>
         <v>0.39937694704049842</v>
       </c>
-      <c r="Q92">
+      <c r="P92">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>112</v>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1913</v>
       </c>
       <c r="B93">
-        <v>1913</v>
+        <v>1612</v>
       </c>
       <c r="C93">
-        <v>1612</v>
+        <v>1573</v>
       </c>
       <c r="D93">
-        <v>1573</v>
+        <v>39</v>
       </c>
       <c r="E93">
-        <v>39</v>
+        <v>659</v>
       </c>
       <c r="F93">
         <v>659</v>
       </c>
       <c r="G93">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="I93">
         <v>612</v>
       </c>
       <c r="J93">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>0.92867981790591803</v>
       </c>
       <c r="L93">
         <v>0.92867981790591803</v>
       </c>
       <c r="M93">
-        <v>0.92867981790591803</v>
+        <v>0</v>
       </c>
       <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
         <f t="shared" si="6"/>
         <v>0.37965260545905705</v>
       </c>
-      <c r="P93">
+      <c r="O93">
         <f t="shared" si="7"/>
         <v>0.38906547997457086</v>
       </c>
-      <c r="Q93">
+      <c r="P93">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>113</v>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>1913</v>
       </c>
       <c r="B94">
-        <v>1913</v>
+        <v>1598</v>
       </c>
       <c r="C94">
-        <v>1598</v>
+        <v>1576</v>
       </c>
       <c r="D94">
-        <v>1576</v>
+        <v>22</v>
       </c>
       <c r="E94">
-        <v>22</v>
+        <v>710</v>
       </c>
       <c r="F94">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G94">
-        <v>708</v>
+        <v>2</v>
       </c>
       <c r="H94">
+        <v>654</v>
+      </c>
+      <c r="I94">
+        <v>652</v>
+      </c>
+      <c r="J94">
         <v>2</v>
       </c>
-      <c r="I94">
-        <v>654</v>
-      </c>
-      <c r="J94">
-        <v>652</v>
-      </c>
       <c r="K94">
-        <v>2</v>
+        <v>0.92112676056338028</v>
       </c>
       <c r="L94">
-        <v>0.92112676056338028</v>
+        <v>0.92090395480225984</v>
       </c>
       <c r="M94">
-        <v>0.92090395480225984</v>
+        <v>1</v>
       </c>
       <c r="N94">
-        <v>1</v>
-      </c>
-      <c r="O94">
         <f t="shared" si="6"/>
         <v>0.40926157697121401</v>
       </c>
-      <c r="P94">
+      <c r="O94">
         <f t="shared" si="7"/>
         <v>0.4137055837563452</v>
       </c>
-      <c r="Q94">
+      <c r="P94">
         <f t="shared" si="8"/>
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>114</v>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>1913</v>
       </c>
       <c r="B95">
-        <v>1913</v>
+        <v>1621</v>
       </c>
       <c r="C95">
-        <v>1621</v>
+        <v>1589</v>
       </c>
       <c r="D95">
-        <v>1589</v>
+        <v>32</v>
       </c>
       <c r="E95">
-        <v>32</v>
+        <v>629</v>
       </c>
       <c r="F95">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G95">
-        <v>628</v>
+        <v>1</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>593</v>
       </c>
       <c r="I95">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J95">
-        <v>592</v>
+        <v>1</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>0.94276629570747217</v>
       </c>
       <c r="L95">
-        <v>0.94276629570747217</v>
+        <v>0.9426751592356688</v>
       </c>
       <c r="M95">
-        <v>0.9426751592356688</v>
+        <v>1</v>
       </c>
       <c r="N95">
-        <v>1</v>
-      </c>
-      <c r="O95">
         <f t="shared" si="6"/>
         <v>0.36582356570018509</v>
       </c>
-      <c r="P95">
+      <c r="O95">
         <f t="shared" si="7"/>
         <v>0.37256135934550033</v>
       </c>
-      <c r="Q95">
+      <c r="P95">
         <f t="shared" si="8"/>
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>115</v>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>1913</v>
       </c>
       <c r="B96">
-        <v>1913</v>
+        <v>1620</v>
       </c>
       <c r="C96">
-        <v>1620</v>
+        <v>1589</v>
       </c>
       <c r="D96">
-        <v>1589</v>
+        <v>31</v>
       </c>
       <c r="E96">
-        <v>31</v>
+        <v>690</v>
       </c>
       <c r="F96">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G96">
-        <v>689</v>
+        <v>1</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>643</v>
       </c>
       <c r="I96">
         <v>643</v>
       </c>
       <c r="J96">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>0.93188405797101448</v>
       </c>
       <c r="L96">
-        <v>0.93188405797101448</v>
+        <v>0.93323657474600874</v>
       </c>
       <c r="M96">
-        <v>0.93323657474600874</v>
+        <v>0</v>
       </c>
       <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
         <f t="shared" si="6"/>
         <v>0.39691358024691359</v>
       </c>
-      <c r="P96">
+      <c r="O96">
         <f t="shared" si="7"/>
         <v>0.40465701699181877</v>
       </c>
-      <c r="Q96">
+      <c r="P96">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>116</v>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>1913</v>
       </c>
       <c r="B97">
-        <v>1913</v>
+        <v>1608</v>
       </c>
       <c r="C97">
-        <v>1608</v>
+        <v>1577</v>
       </c>
       <c r="D97">
-        <v>1577</v>
+        <v>31</v>
       </c>
       <c r="E97">
-        <v>31</v>
+        <v>720</v>
       </c>
       <c r="F97">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G97">
-        <v>719</v>
+        <v>1</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>664</v>
       </c>
       <c r="I97">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J97">
-        <v>663</v>
+        <v>1</v>
       </c>
       <c r="K97">
-        <v>1</v>
+        <v>0.92222222222222228</v>
       </c>
       <c r="L97">
-        <v>0.92222222222222228</v>
+        <v>0.92211404728789981</v>
       </c>
       <c r="M97">
-        <v>0.92211404728789981</v>
+        <v>1</v>
       </c>
       <c r="N97">
-        <v>1</v>
-      </c>
-      <c r="O97">
         <f t="shared" si="6"/>
         <v>0.41293532338308458</v>
       </c>
-      <c r="P97">
+      <c r="O97">
         <f t="shared" si="7"/>
         <v>0.42041851616994291</v>
       </c>
-      <c r="Q97">
+      <c r="P97">
         <f t="shared" si="8"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>117</v>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>1913</v>
       </c>
       <c r="B98">
-        <v>1913</v>
+        <v>1611</v>
       </c>
       <c r="C98">
-        <v>1611</v>
+        <v>1578</v>
       </c>
       <c r="D98">
-        <v>1578</v>
+        <v>33</v>
       </c>
       <c r="E98">
-        <v>33</v>
+        <v>672</v>
       </c>
       <c r="F98">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G98">
-        <v>671</v>
+        <v>1</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>624</v>
       </c>
       <c r="I98">
         <v>624</v>
       </c>
       <c r="J98">
-        <v>624</v>
+        <v>0</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="L98">
-        <v>0.9285714285714286</v>
+        <v>0.92995529061102833</v>
       </c>
       <c r="M98">
-        <v>0.92995529061102833</v>
+        <v>0</v>
       </c>
       <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
         <f t="shared" si="6"/>
         <v>0.38733705772811916</v>
       </c>
-      <c r="P98">
+      <c r="O98">
         <f t="shared" si="7"/>
         <v>0.39543726235741444</v>
       </c>
-      <c r="Q98">
+      <c r="P98">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>118</v>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>1913</v>
       </c>
       <c r="B99">
-        <v>1913</v>
+        <v>1626</v>
       </c>
       <c r="C99">
-        <v>1626</v>
+        <v>1590</v>
       </c>
       <c r="D99">
-        <v>1590</v>
+        <v>36</v>
       </c>
       <c r="E99">
-        <v>36</v>
+        <v>685</v>
       </c>
       <c r="F99">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G99">
-        <v>683</v>
+        <v>2</v>
       </c>
       <c r="H99">
-        <v>2</v>
+        <v>634</v>
       </c>
       <c r="I99">
         <v>634</v>
       </c>
       <c r="J99">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>0.9255474452554745</v>
       </c>
       <c r="L99">
-        <v>0.9255474452554745</v>
+        <v>0.9282576866764275</v>
       </c>
       <c r="M99">
-        <v>0.9282576866764275</v>
+        <v>0</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <f t="shared" ref="N99:N112" si="9">H99/B99</f>
+        <v>0.38991389913899138</v>
       </c>
       <c r="O99">
-        <f t="shared" ref="O99:O112" si="9">I99/C99</f>
-        <v>0.38991389913899138</v>
+        <f t="shared" ref="O99:O112" si="10">I99/C99</f>
+        <v>0.3987421383647799</v>
       </c>
       <c r="P99">
-        <f t="shared" ref="P99:P112" si="10">J99/D99</f>
-        <v>0.3987421383647799</v>
-      </c>
-      <c r="Q99">
-        <f t="shared" ref="Q99:Q112" si="11">K99/E99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>119</v>
+        <f t="shared" ref="P99:P112" si="11">J99/D99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>1913</v>
       </c>
       <c r="B100">
-        <v>1913</v>
+        <v>1636</v>
       </c>
       <c r="C100">
-        <v>1636</v>
+        <v>1605</v>
       </c>
       <c r="D100">
-        <v>1605</v>
+        <v>31</v>
       </c>
       <c r="E100">
-        <v>31</v>
+        <v>688</v>
       </c>
       <c r="F100">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G100">
-        <v>686</v>
+        <v>2</v>
       </c>
       <c r="H100">
-        <v>2</v>
+        <v>629</v>
       </c>
       <c r="I100">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J100">
-        <v>628</v>
+        <v>1</v>
       </c>
       <c r="K100">
-        <v>1</v>
+        <v>0.91424418604651159</v>
       </c>
       <c r="L100">
-        <v>0.91424418604651159</v>
+        <v>0.91545189504373181</v>
       </c>
       <c r="M100">
-        <v>0.91545189504373181</v>
+        <v>0.5</v>
       </c>
       <c r="N100">
-        <v>0.5</v>
-      </c>
-      <c r="O100">
         <f t="shared" si="9"/>
         <v>0.38447432762836187</v>
       </c>
-      <c r="P100">
+      <c r="O100">
         <f t="shared" si="10"/>
         <v>0.3912772585669782</v>
       </c>
-      <c r="Q100">
+      <c r="P100">
         <f t="shared" si="11"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>122</v>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>1913</v>
       </c>
       <c r="B101">
-        <v>1913</v>
+        <v>1631</v>
       </c>
       <c r="C101">
-        <v>1631</v>
+        <v>1595</v>
       </c>
       <c r="D101">
-        <v>1595</v>
+        <v>36</v>
       </c>
       <c r="E101">
-        <v>36</v>
+        <v>669</v>
       </c>
       <c r="F101">
         <v>669</v>
       </c>
       <c r="G101">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="I101">
         <v>632</v>
       </c>
       <c r="J101">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>0.94469357249626307</v>
       </c>
       <c r="L101">
         <v>0.94469357249626307</v>
       </c>
       <c r="M101">
-        <v>0.94469357249626307</v>
+        <v>0</v>
       </c>
       <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
         <f t="shared" si="9"/>
         <v>0.38749233599019006</v>
       </c>
-      <c r="P101">
+      <c r="O101">
         <f t="shared" si="10"/>
         <v>0.39623824451410661</v>
       </c>
-      <c r="Q101">
+      <c r="P101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>123</v>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>1913</v>
       </c>
       <c r="B102">
-        <v>1913</v>
+        <v>1620</v>
       </c>
       <c r="C102">
-        <v>1620</v>
+        <v>1608</v>
       </c>
       <c r="D102">
-        <v>1608</v>
+        <v>12</v>
       </c>
       <c r="E102">
-        <v>12</v>
+        <v>693</v>
       </c>
       <c r="F102">
         <v>693</v>
       </c>
       <c r="G102">
-        <v>693</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="I102">
         <v>638</v>
       </c>
       <c r="J102">
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>0.92063492063492058</v>
       </c>
       <c r="L102">
         <v>0.92063492063492058</v>
       </c>
       <c r="M102">
-        <v>0.92063492063492058</v>
+        <v>0</v>
       </c>
       <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
         <f t="shared" si="9"/>
         <v>0.39382716049382716</v>
       </c>
-      <c r="P102">
+      <c r="O102">
         <f t="shared" si="10"/>
         <v>0.39676616915422885</v>
       </c>
-      <c r="Q102">
+      <c r="P102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>14</v>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>4783</v>
       </c>
       <c r="B103">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C103">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D103">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E103">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F103">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G103">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I103">
         <v>1561</v>
       </c>
       <c r="J103">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L103">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M103">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P103">
+      <c r="O103">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q103">
+      <c r="P103">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>21</v>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>4783</v>
       </c>
       <c r="B104">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C104">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D104">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E104">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F104">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G104">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H104">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I104">
         <v>1561</v>
       </c>
       <c r="J104">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L104">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M104">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P104">
+      <c r="O104">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q104">
+      <c r="P104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>42</v>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>4783</v>
       </c>
       <c r="B105">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C105">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D105">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E105">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F105">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G105">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H105">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I105">
         <v>1561</v>
       </c>
       <c r="J105">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L105">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M105">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="O105">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P105">
+      <c r="O105">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q105">
+      <c r="P105">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>49</v>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>4783</v>
       </c>
       <c r="B106">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C106">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D106">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E106">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F106">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G106">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H106">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I106">
         <v>1561</v>
       </c>
       <c r="J106">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L106">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M106">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P106">
+      <c r="O106">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q106">
+      <c r="P106">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>53</v>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>4783</v>
       </c>
       <c r="B107">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C107">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D107">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E107">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F107">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G107">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H107">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I107">
         <v>1561</v>
       </c>
       <c r="J107">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L107">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M107">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N107">
-        <v>0</v>
-      </c>
-      <c r="O107">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P107">
+      <c r="O107">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q107">
+      <c r="P107">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>55</v>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>4783</v>
       </c>
       <c r="B108">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C108">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D108">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E108">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F108">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G108">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H108">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I108">
         <v>1561</v>
       </c>
       <c r="J108">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L108">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M108">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P108">
+      <c r="O108">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q108">
+      <c r="P108">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>65</v>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>4783</v>
       </c>
       <c r="B109">
-        <v>4783</v>
+        <v>4088</v>
       </c>
       <c r="C109">
-        <v>4088</v>
+        <v>4063</v>
       </c>
       <c r="D109">
-        <v>4063</v>
+        <v>25</v>
       </c>
       <c r="E109">
-        <v>25</v>
+        <v>1687</v>
       </c>
       <c r="F109">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G109">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H109">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I109">
         <v>1561</v>
       </c>
       <c r="J109">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L109">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M109">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
         <f t="shared" si="9"/>
         <v>0.38184931506849318</v>
       </c>
-      <c r="P109">
+      <c r="O109">
         <f t="shared" si="10"/>
         <v>0.38419886783165147</v>
       </c>
-      <c r="Q109">
+      <c r="P109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>90</v>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>4783</v>
       </c>
       <c r="B110">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C110">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D110">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E110">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F110">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G110">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H110">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I110">
         <v>1561</v>
       </c>
       <c r="J110">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L110">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M110">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>0</v>
-      </c>
-      <c r="O110">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P110">
+      <c r="O110">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q110">
+      <c r="P110">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>107</v>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>4783</v>
       </c>
       <c r="B111">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C111">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D111">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E111">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F111">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G111">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H111">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I111">
         <v>1561</v>
       </c>
       <c r="J111">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L111">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M111">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P111">
+      <c r="O111">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q111">
+      <c r="P111">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>120</v>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>4783</v>
       </c>
       <c r="B112">
-        <v>4783</v>
+        <v>4048</v>
       </c>
       <c r="C112">
-        <v>4048</v>
+        <v>3997</v>
       </c>
       <c r="D112">
-        <v>3997</v>
+        <v>51</v>
       </c>
       <c r="E112">
-        <v>51</v>
+        <v>1687</v>
       </c>
       <c r="F112">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G112">
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I112">
         <v>1561</v>
       </c>
       <c r="J112">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L112">
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M112">
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
         <f t="shared" si="9"/>
         <v>0.3856225296442688</v>
       </c>
-      <c r="P112">
+      <c r="O112">
         <f t="shared" si="10"/>
         <v>0.39054290718038531</v>
       </c>
-      <c r="Q112">
+      <c r="P112">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>127</v>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <f>AVERAGE(A103:A112)</f>
+        <v>4783</v>
       </c>
       <c r="B115">
         <f>AVERAGE(B103:B112)</f>
-        <v>4783</v>
+        <v>4052</v>
       </c>
       <c r="C115">
-        <f>AVERAGE(C103:C112)</f>
-        <v>4052</v>
+        <f t="shared" ref="C115:P115" si="12">AVERAGE(C103:C112)</f>
+        <v>4003.6</v>
       </c>
       <c r="D115">
-        <f t="shared" ref="D115:Q115" si="12">AVERAGE(D103:D112)</f>
-        <v>4003.6</v>
+        <f t="shared" si="12"/>
+        <v>48.4</v>
       </c>
       <c r="E115">
         <f t="shared" si="12"/>
-        <v>48.4</v>
+        <v>1687</v>
       </c>
       <c r="F115">
         <f t="shared" si="12"/>
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="G115">
         <f t="shared" si="12"/>
-        <v>1685</v>
+        <v>2</v>
       </c>
       <c r="H115">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1561</v>
       </c>
       <c r="I115">
         <f t="shared" si="12"/>
@@ -7059,110 +6393,109 @@
       </c>
       <c r="J115">
         <f t="shared" si="12"/>
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K115">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.92531120331950212</v>
       </c>
       <c r="L115">
         <f t="shared" si="12"/>
-        <v>0.92531120331950212</v>
+        <v>0.92640949554896146</v>
       </c>
       <c r="M115">
         <f t="shared" si="12"/>
-        <v>0.92640949554896146</v>
+        <v>0</v>
       </c>
       <c r="N115">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.38524520818669117</v>
       </c>
       <c r="O115">
         <f t="shared" si="12"/>
-        <v>0.38524520818669117</v>
+        <v>0.38990850324551196</v>
       </c>
       <c r="P115">
         <f t="shared" si="12"/>
-        <v>0.38990850324551196</v>
-      </c>
-      <c r="Q115">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>128</v>
+        <v>0</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <f>AVERAGE(A3:A102)</f>
+        <v>1912.9</v>
       </c>
       <c r="B116">
-        <f>AVERAGE(B3:B102)</f>
-        <v>1912.9</v>
+        <f t="shared" ref="B116:P116" si="13">AVERAGE(B3:B102)</f>
+        <v>1616.5</v>
       </c>
       <c r="C116">
-        <f t="shared" ref="C116:Q116" si="13">AVERAGE(C3:C102)</f>
-        <v>1616.5</v>
+        <f t="shared" si="13"/>
+        <v>1589.34</v>
       </c>
       <c r="D116">
         <f t="shared" si="13"/>
-        <v>1589.34</v>
+        <v>27.16</v>
       </c>
       <c r="E116">
         <f t="shared" si="13"/>
-        <v>27.16</v>
+        <v>692.2</v>
       </c>
       <c r="F116">
         <f t="shared" si="13"/>
-        <v>692.2</v>
+        <v>691.13</v>
       </c>
       <c r="G116">
         <f t="shared" si="13"/>
-        <v>691.13</v>
+        <v>1.07</v>
       </c>
       <c r="H116">
         <f t="shared" si="13"/>
-        <v>1.07</v>
+        <v>641.09</v>
       </c>
       <c r="I116">
         <f t="shared" si="13"/>
-        <v>641.09</v>
+        <v>640.45000000000005</v>
       </c>
       <c r="J116">
         <f t="shared" si="13"/>
-        <v>640.45000000000005</v>
+        <v>0.64</v>
       </c>
       <c r="K116">
         <f t="shared" si="13"/>
-        <v>0.64</v>
+        <v>0.92637758387128288</v>
       </c>
       <c r="L116">
         <f t="shared" si="13"/>
-        <v>0.92637758387128288</v>
+        <v>0.92687939310530154</v>
       </c>
       <c r="M116">
         <f t="shared" si="13"/>
-        <v>0.92687939310530154</v>
+        <v>0.38850000000000001</v>
       </c>
       <c r="N116">
         <f t="shared" si="13"/>
-        <v>0.38850000000000001</v>
+        <v>0.39666086047024651</v>
       </c>
       <c r="O116">
         <f t="shared" si="13"/>
-        <v>0.39666086047024651</v>
+        <v>0.40304906004926666</v>
       </c>
       <c r="P116">
         <f t="shared" si="13"/>
-        <v>0.40304906004926666</v>
-      </c>
-      <c r="Q116">
-        <f t="shared" si="13"/>
         <v>2.5936622902027605E-2</v>
       </c>
+      <c r="Q116" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q2" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q112">
-      <sortCondition ref="B2"/>
+  <autoFilter ref="A2:P2" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P112">
+      <sortCondition ref="A2"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_9.xlsx
+++ b/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_QT_detailed_results_0_9.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\LApredict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14338F06-5597-4E18-AB99-2C6E6EB7C6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D62A00-C9C9-469F-A6BB-D71B49D25AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33890" yWindow="8680" windowWidth="23660" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="valid" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">valid!$A$2:$P$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>Total Rows</t>
   </si>
@@ -84,9 +85,6 @@
   </si>
   <si>
     <t>recall fault-prone</t>
-  </si>
-  <si>
-    <t>Test avg</t>
   </si>
   <si>
     <t>Valid avg</t>
@@ -146,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -154,6 +152,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1913</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1913</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1913</v>
       </c>
@@ -5653,19 +5653,19 @@
         <v>0</v>
       </c>
       <c r="N99">
-        <f t="shared" ref="N99:N112" si="9">H99/B99</f>
+        <f t="shared" ref="N99:N102" si="9">H99/B99</f>
         <v>0.38991389913899138</v>
       </c>
       <c r="O99">
-        <f t="shared" ref="O99:O112" si="10">I99/C99</f>
+        <f t="shared" ref="O99:O102" si="10">I99/C99</f>
         <v>0.3987421383647799</v>
       </c>
       <c r="P99">
-        <f t="shared" ref="P99:P112" si="11">J99/D99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+        <f t="shared" ref="P99:P102" si="11">J99/D99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1913</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1913</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1913</v>
       </c>
@@ -5824,672 +5824,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>4783</v>
-      </c>
-      <c r="B103">
-        <v>4048</v>
-      </c>
-      <c r="C103">
-        <v>3997</v>
-      </c>
-      <c r="D103">
-        <v>51</v>
-      </c>
-      <c r="E103">
-        <v>1687</v>
-      </c>
-      <c r="F103">
-        <v>1685</v>
-      </c>
-      <c r="G103">
-        <v>2</v>
-      </c>
-      <c r="H103">
-        <v>1561</v>
-      </c>
-      <c r="I103">
-        <v>1561</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L103">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O103">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P103">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>4783</v>
-      </c>
-      <c r="B104">
-        <v>4048</v>
-      </c>
-      <c r="C104">
-        <v>3997</v>
-      </c>
-      <c r="D104">
-        <v>51</v>
-      </c>
-      <c r="E104">
-        <v>1687</v>
-      </c>
-      <c r="F104">
-        <v>1685</v>
-      </c>
-      <c r="G104">
-        <v>2</v>
-      </c>
-      <c r="H104">
-        <v>1561</v>
-      </c>
-      <c r="I104">
-        <v>1561</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L104">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O104">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P104">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>4783</v>
-      </c>
-      <c r="B105">
-        <v>4048</v>
-      </c>
-      <c r="C105">
-        <v>3997</v>
-      </c>
-      <c r="D105">
-        <v>51</v>
-      </c>
-      <c r="E105">
-        <v>1687</v>
-      </c>
-      <c r="F105">
-        <v>1685</v>
-      </c>
-      <c r="G105">
-        <v>2</v>
-      </c>
-      <c r="H105">
-        <v>1561</v>
-      </c>
-      <c r="I105">
-        <v>1561</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L105">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O105">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P105">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>4783</v>
-      </c>
-      <c r="B106">
-        <v>4048</v>
-      </c>
-      <c r="C106">
-        <v>3997</v>
-      </c>
-      <c r="D106">
-        <v>51</v>
-      </c>
-      <c r="E106">
-        <v>1687</v>
-      </c>
-      <c r="F106">
-        <v>1685</v>
-      </c>
-      <c r="G106">
-        <v>2</v>
-      </c>
-      <c r="H106">
-        <v>1561</v>
-      </c>
-      <c r="I106">
-        <v>1561</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L106">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O106">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P106">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>4783</v>
-      </c>
-      <c r="B107">
-        <v>4048</v>
-      </c>
-      <c r="C107">
-        <v>3997</v>
-      </c>
-      <c r="D107">
-        <v>51</v>
-      </c>
-      <c r="E107">
-        <v>1687</v>
-      </c>
-      <c r="F107">
-        <v>1685</v>
-      </c>
-      <c r="G107">
-        <v>2</v>
-      </c>
-      <c r="H107">
-        <v>1561</v>
-      </c>
-      <c r="I107">
-        <v>1561</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L107">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O107">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P107">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>4783</v>
-      </c>
-      <c r="B108">
-        <v>4048</v>
-      </c>
-      <c r="C108">
-        <v>3997</v>
-      </c>
-      <c r="D108">
-        <v>51</v>
-      </c>
-      <c r="E108">
-        <v>1687</v>
-      </c>
-      <c r="F108">
-        <v>1685</v>
-      </c>
-      <c r="G108">
-        <v>2</v>
-      </c>
-      <c r="H108">
-        <v>1561</v>
-      </c>
-      <c r="I108">
-        <v>1561</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L108">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O108">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P108">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>4783</v>
-      </c>
-      <c r="B109">
-        <v>4088</v>
-      </c>
-      <c r="C109">
-        <v>4063</v>
-      </c>
-      <c r="D109">
-        <v>25</v>
-      </c>
-      <c r="E109">
-        <v>1687</v>
-      </c>
-      <c r="F109">
-        <v>1685</v>
-      </c>
-      <c r="G109">
-        <v>2</v>
-      </c>
-      <c r="H109">
-        <v>1561</v>
-      </c>
-      <c r="I109">
-        <v>1561</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L109">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109">
-        <f t="shared" si="9"/>
-        <v>0.38184931506849318</v>
-      </c>
-      <c r="O109">
-        <f t="shared" si="10"/>
-        <v>0.38419886783165147</v>
-      </c>
-      <c r="P109">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>4783</v>
-      </c>
-      <c r="B110">
-        <v>4048</v>
-      </c>
-      <c r="C110">
-        <v>3997</v>
-      </c>
-      <c r="D110">
-        <v>51</v>
-      </c>
-      <c r="E110">
-        <v>1687</v>
-      </c>
-      <c r="F110">
-        <v>1685</v>
-      </c>
-      <c r="G110">
-        <v>2</v>
-      </c>
-      <c r="H110">
-        <v>1561</v>
-      </c>
-      <c r="I110">
-        <v>1561</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L110">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O110">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P110">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>4783</v>
-      </c>
-      <c r="B111">
-        <v>4048</v>
-      </c>
-      <c r="C111">
-        <v>3997</v>
-      </c>
-      <c r="D111">
-        <v>51</v>
-      </c>
-      <c r="E111">
-        <v>1687</v>
-      </c>
-      <c r="F111">
-        <v>1685</v>
-      </c>
-      <c r="G111">
-        <v>2</v>
-      </c>
-      <c r="H111">
-        <v>1561</v>
-      </c>
-      <c r="I111">
-        <v>1561</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L111">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O111">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P111">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>4783</v>
-      </c>
-      <c r="B112">
-        <v>4048</v>
-      </c>
-      <c r="C112">
-        <v>3997</v>
-      </c>
-      <c r="D112">
-        <v>51</v>
-      </c>
-      <c r="E112">
-        <v>1687</v>
-      </c>
-      <c r="F112">
-        <v>1685</v>
-      </c>
-      <c r="G112">
-        <v>2</v>
-      </c>
-      <c r="H112">
-        <v>1561</v>
-      </c>
-      <c r="I112">
-        <v>1561</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L112">
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <f t="shared" si="9"/>
-        <v>0.3856225296442688</v>
-      </c>
-      <c r="O112">
-        <f t="shared" si="10"/>
-        <v>0.39054290718038531</v>
-      </c>
-      <c r="P112">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <f>AVERAGE(A103:A112)</f>
-        <v>4783</v>
-      </c>
-      <c r="B115">
-        <f>AVERAGE(B103:B112)</f>
-        <v>4052</v>
-      </c>
-      <c r="C115">
-        <f t="shared" ref="C115:P115" si="12">AVERAGE(C103:C112)</f>
-        <v>4003.6</v>
-      </c>
-      <c r="D115">
-        <f t="shared" si="12"/>
-        <v>48.4</v>
-      </c>
-      <c r="E115">
-        <f t="shared" si="12"/>
-        <v>1687</v>
-      </c>
-      <c r="F115">
-        <f t="shared" si="12"/>
-        <v>1685</v>
-      </c>
-      <c r="G115">
-        <f t="shared" si="12"/>
-        <v>2</v>
-      </c>
-      <c r="H115">
-        <f t="shared" si="12"/>
-        <v>1561</v>
-      </c>
-      <c r="I115">
-        <f t="shared" si="12"/>
-        <v>1561</v>
-      </c>
-      <c r="J115">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <f t="shared" si="12"/>
-        <v>0.92531120331950212</v>
-      </c>
-      <c r="L115">
-        <f t="shared" si="12"/>
-        <v>0.92640949554896146</v>
-      </c>
-      <c r="M115">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N115">
-        <f t="shared" si="12"/>
-        <v>0.38524520818669117</v>
-      </c>
-      <c r="O115">
-        <f t="shared" si="12"/>
-        <v>0.38990850324551196</v>
-      </c>
-      <c r="P115">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A116">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A105" s="3">
         <f>AVERAGE(A3:A102)</f>
         <v>1912.9</v>
       </c>
-      <c r="B116">
-        <f t="shared" ref="B116:P116" si="13">AVERAGE(B3:B102)</f>
+      <c r="B105" s="3">
+        <f t="shared" ref="B105:P105" si="12">AVERAGE(B3:B102)</f>
         <v>1616.5</v>
       </c>
-      <c r="C116">
-        <f t="shared" si="13"/>
+      <c r="C105" s="3">
+        <f t="shared" si="12"/>
         <v>1589.34</v>
       </c>
-      <c r="D116">
-        <f t="shared" si="13"/>
+      <c r="D105" s="3">
+        <f t="shared" si="12"/>
         <v>27.16</v>
       </c>
-      <c r="E116">
-        <f t="shared" si="13"/>
+      <c r="E105" s="3">
+        <f t="shared" si="12"/>
         <v>692.2</v>
       </c>
-      <c r="F116">
-        <f t="shared" si="13"/>
+      <c r="F105" s="3">
+        <f t="shared" si="12"/>
         <v>691.13</v>
       </c>
-      <c r="G116">
-        <f t="shared" si="13"/>
+      <c r="G105" s="3">
+        <f t="shared" si="12"/>
         <v>1.07</v>
       </c>
-      <c r="H116">
-        <f t="shared" si="13"/>
+      <c r="H105" s="3">
+        <f t="shared" si="12"/>
         <v>641.09</v>
       </c>
-      <c r="I116">
-        <f t="shared" si="13"/>
+      <c r="I105" s="3">
+        <f t="shared" si="12"/>
         <v>640.45000000000005</v>
       </c>
-      <c r="J116">
-        <f t="shared" si="13"/>
+      <c r="J105" s="3">
+        <f t="shared" si="12"/>
         <v>0.64</v>
       </c>
-      <c r="K116">
-        <f t="shared" si="13"/>
+      <c r="K105" s="4">
+        <f t="shared" si="12"/>
         <v>0.92637758387128288</v>
       </c>
-      <c r="L116">
-        <f t="shared" si="13"/>
+      <c r="L105" s="4">
+        <f t="shared" si="12"/>
         <v>0.92687939310530154</v>
       </c>
-      <c r="M116">
-        <f t="shared" si="13"/>
+      <c r="M105" s="4">
+        <f t="shared" si="12"/>
         <v>0.38850000000000001</v>
       </c>
-      <c r="N116">
-        <f t="shared" si="13"/>
+      <c r="N105" s="4">
+        <f t="shared" si="12"/>
         <v>0.39666086047024651</v>
       </c>
-      <c r="O116">
-        <f t="shared" si="13"/>
+      <c r="O105" s="4">
+        <f t="shared" si="12"/>
         <v>0.40304906004926666</v>
       </c>
-      <c r="P116">
-        <f t="shared" si="13"/>
+      <c r="P105" s="4">
+        <f t="shared" si="12"/>
         <v>2.5936622902027605E-2</v>
       </c>
-      <c r="Q116" t="s">
-        <v>17</v>
+      <c r="Q105" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6500,4 +5901,660 @@
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96F5FBA-7C10-43EC-9781-594735355AF0}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4783</v>
+      </c>
+      <c r="B2">
+        <v>4048</v>
+      </c>
+      <c r="C2">
+        <v>3997</v>
+      </c>
+      <c r="D2">
+        <v>51</v>
+      </c>
+      <c r="E2">
+        <v>1687</v>
+      </c>
+      <c r="F2">
+        <v>1685</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1561</v>
+      </c>
+      <c r="I2">
+        <v>1561</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L2">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:P11" si="0">H2/B2</f>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4783</v>
+      </c>
+      <c r="B3">
+        <v>4048</v>
+      </c>
+      <c r="C3">
+        <v>3997</v>
+      </c>
+      <c r="D3">
+        <v>51</v>
+      </c>
+      <c r="E3">
+        <v>1687</v>
+      </c>
+      <c r="F3">
+        <v>1685</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1561</v>
+      </c>
+      <c r="I3">
+        <v>1561</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L3">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4783</v>
+      </c>
+      <c r="B4">
+        <v>4048</v>
+      </c>
+      <c r="C4">
+        <v>3997</v>
+      </c>
+      <c r="D4">
+        <v>51</v>
+      </c>
+      <c r="E4">
+        <v>1687</v>
+      </c>
+      <c r="F4">
+        <v>1685</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1561</v>
+      </c>
+      <c r="I4">
+        <v>1561</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L4">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4783</v>
+      </c>
+      <c r="B5">
+        <v>4048</v>
+      </c>
+      <c r="C5">
+        <v>3997</v>
+      </c>
+      <c r="D5">
+        <v>51</v>
+      </c>
+      <c r="E5">
+        <v>1687</v>
+      </c>
+      <c r="F5">
+        <v>1685</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1561</v>
+      </c>
+      <c r="I5">
+        <v>1561</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L5">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4783</v>
+      </c>
+      <c r="B6">
+        <v>4048</v>
+      </c>
+      <c r="C6">
+        <v>3997</v>
+      </c>
+      <c r="D6">
+        <v>51</v>
+      </c>
+      <c r="E6">
+        <v>1687</v>
+      </c>
+      <c r="F6">
+        <v>1685</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1561</v>
+      </c>
+      <c r="I6">
+        <v>1561</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L6">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4783</v>
+      </c>
+      <c r="B7">
+        <v>4048</v>
+      </c>
+      <c r="C7">
+        <v>3997</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>1687</v>
+      </c>
+      <c r="F7">
+        <v>1685</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>1561</v>
+      </c>
+      <c r="I7">
+        <v>1561</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L7">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>4783</v>
+      </c>
+      <c r="B8">
+        <v>4088</v>
+      </c>
+      <c r="C8">
+        <v>4063</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>1687</v>
+      </c>
+      <c r="F8">
+        <v>1685</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>1561</v>
+      </c>
+      <c r="I8">
+        <v>1561</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L8">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>0.38184931506849318</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>0.38419886783165147</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4783</v>
+      </c>
+      <c r="B9">
+        <v>4048</v>
+      </c>
+      <c r="C9">
+        <v>3997</v>
+      </c>
+      <c r="D9">
+        <v>51</v>
+      </c>
+      <c r="E9">
+        <v>1687</v>
+      </c>
+      <c r="F9">
+        <v>1685</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>1561</v>
+      </c>
+      <c r="I9">
+        <v>1561</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L9">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>4783</v>
+      </c>
+      <c r="B10">
+        <v>4048</v>
+      </c>
+      <c r="C10">
+        <v>3997</v>
+      </c>
+      <c r="D10">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <v>1687</v>
+      </c>
+      <c r="F10">
+        <v>1685</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>1561</v>
+      </c>
+      <c r="I10">
+        <v>1561</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L10">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>4783</v>
+      </c>
+      <c r="B11">
+        <v>4048</v>
+      </c>
+      <c r="C11">
+        <v>3997</v>
+      </c>
+      <c r="D11">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>1687</v>
+      </c>
+      <c r="F11">
+        <v>1685</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>1561</v>
+      </c>
+      <c r="I11">
+        <v>1561</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L11">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>0.3856225296442688</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>0.39054290718038531</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f>AVERAGE(A2:A11)</f>
+        <v>4783</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ref="B13:P13" si="1">AVERAGE(B2:B11)</f>
+        <v>4052</v>
+      </c>
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>4003.6</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="1"/>
+        <v>48.4</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>1687</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>1685</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>1561</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>1561</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="1"/>
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="1"/>
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <f t="shared" si="1"/>
+        <v>0.38524520818669117</v>
+      </c>
+      <c r="O13" s="4">
+        <f t="shared" si="1"/>
+        <v>0.38990850324551196</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>